--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -933,7 +933,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Segunda-feira, 10 minutos: conferir o extrato, marcar as pagas, mandar as mensagens da lista "Cobrar primeiro". Sexta: lembrar quem vence na semana seguinte.</t>
+          <t>Sexta-feira, 4 minutos (rotina da semana, planilha 03): conferir o extrato, marcar as parcelas pagas, mandar as mensagens da lista "Cobrar primeiro" e lembrar quem vence na semana seguinte. Tudo numa passada só, na sexta.</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
         <f>SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"A vencer",Parcelas!$K$5:$K$404,"&lt;="&amp;Config!$B$6)</f>
-        <v>1360</v>
+        <v>970</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
         <f>SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"A vencer",Parcelas!$K$5:$K$404,"&lt;="&amp;Config!$B$7)</f>
-        <v>5090</v>
+        <v>4705</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="14">
         <f>SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"A vencer")+SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"Vencida")</f>
-        <v>10585</v>
+        <v>9855</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="15">
         <f>SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"Vencida")</f>
-        <v>4550</v>
+        <v>3775</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="16">
         <f>COUNTIFS(Parcelas!$I$5:$I$404,"Vencida")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="17">
         <f>IFERROR(G5/(G5+SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$I$5:$I$404,"Paga")),0)</f>
-        <v>0.104465618183905</v>
+        <v>0.0935795736241944</v>
       </c>
       <c r="L5" s="12" t="n"/>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D11" s="26">
         <f>IF(Config!$C$10="","",IFERROR(C11/$G$5,0))</f>
-        <v>0.0703296703296703</v>
+        <v>0.0847682119205298</v>
       </c>
       <c r="E11" s="27" t="str">
         <f>IF(Config!$C$10="","",Config!$B$10)</f>
@@ -1222,15 +1222,15 @@
       </c>
       <c r="B12" s="24">
         <f>IF(Config!$C$11="","",COUNTIFS(Parcelas!$L$5:$L$404,Config!$C$11))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" s="25">
         <f>IF(Config!$C$11="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$L$5:$L$404,Config!$C$11))</f>
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="D12" s="26">
         <f>IF(Config!$C$11="","",IFERROR(C12/$G$5,0))</f>
-        <v>0.12967032967033</v>
+        <v>0</v>
       </c>
       <c r="E12" s="27" t="str">
         <f>IF(Config!$C$11="","",Config!$B$11)</f>
@@ -1247,15 +1247,15 @@
       </c>
       <c r="B13" s="24">
         <f>IF(Config!$C$12="","",COUNTIFS(Parcelas!$L$5:$L$404,Config!$C$12))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="25">
         <f>IF(Config!$C$12="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$L$5:$L$404,Config!$C$12))</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="D13" s="26">
         <f>IF(Config!$C$12="","",IFERROR(C13/$G$5,0))</f>
-        <v>0.0989010989010989</v>
+        <v>0</v>
       </c>
       <c r="E13" s="27" t="str">
         <f>IF(Config!$C$12="","",Config!$B$12)</f>
@@ -1272,15 +1272,15 @@
       </c>
       <c r="B14" s="24">
         <f>IF(Config!$C$13="","",COUNTIFS(Parcelas!$L$5:$L$404,Config!$C$13))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="25">
         <f>IF(Config!$C$13="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$L$5:$L$404,Config!$C$13))</f>
-        <v>3190</v>
+        <v>3455</v>
       </c>
       <c r="D14" s="26">
         <f>IF(Config!$C$13="","",IFERROR(C14/$G$5,0))</f>
-        <v>0.701098901098901</v>
+        <v>0.91523178807947</v>
       </c>
       <c r="E14" s="27" t="str">
         <f>IF(Config!$C$13="","",Config!$B$13)</f>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,2)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,2),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Regina Teixeira</v>
+        <v>Priscila Reis</v>
       </c>
       <c r="C21" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,2)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,2),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Consulta</v>
+        <v>Avaliação endócrina</v>
       </c>
       <c r="D21" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,2)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$N$5:$N$404,2),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="F21" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,2)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,2),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="G21" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,2)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,2),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B23" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Eduardo Lima</v>
+        <v>Helena Moreira</v>
       </c>
       <c r="C23" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="E23" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46185.0</v>
+        <v>46186.0</v>
       </c>
       <c r="F23" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G23" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H23" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,4)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,4),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B25" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Paulo Reis</v>
+        <v>Mariana Nascimento</v>
       </c>
       <c r="C25" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="E25" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46197.0</v>
+        <v>46192.0</v>
       </c>
       <c r="F25" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G25" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H25" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,6)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,6),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1628,11 +1628,11 @@
       </c>
       <c r="B26" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Otávio Nascimento</v>
+        <v>Mariana Nascimento</v>
       </c>
       <c r="C26" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>MAPA</v>
+        <v>Consulta</v>
       </c>
       <c r="D26" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1640,15 +1640,15 @@
       </c>
       <c r="E26" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46191.0</v>
+        <v>46200.0</v>
       </c>
       <c r="F26" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="G26" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,7)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,7),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B27" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Otávio Cardoso</v>
+        <v>Patrícia Fernandes</v>
       </c>
       <c r="C27" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E27" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46158.0</v>
+        <v>46160.0</v>
       </c>
       <c r="F27" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G27" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H27" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,8)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,8),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B28" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Viviane Ribeiro</v>
+        <v>Rafael Dias</v>
       </c>
       <c r="C28" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1716,19 +1716,19 @@
       </c>
       <c r="D28" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46220.0</v>
+        <v>46165.0</v>
       </c>
       <c r="F28" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G28" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="H28" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,9)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,9),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B29" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>Camila Freitas</v>
+        <v>Cláudia Costa</v>
       </c>
       <c r="C29" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D29" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>46161.0</v>
+        <v>46225.0</v>
       </c>
       <c r="F29" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G29" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$J$5:$J$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="H29" s="24" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$N$5:$N$404,10)&gt;0,INDEX(Parcelas!$L$5:$L$404,MATCH(LARGE(Parcelas!$N$5:$N$404,10),Parcelas!$N$5:$N$404,0)),""),"")</f>
@@ -1926,11 +1926,11 @@
       </c>
       <c r="B37" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Márcia Duarte</v>
+        <v>Eduardo Lima</v>
       </c>
       <c r="C37" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Avaliação endócrina</v>
+        <v>Teste ergométrico</v>
       </c>
       <c r="D37" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -1938,15 +1938,15 @@
       </c>
       <c r="E37" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F37" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G37" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,4)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$O$5:$O$404,4),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B38" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Rafael Barros</v>
+        <v>Cláudia Santos</v>
       </c>
       <c r="C38" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -1963,19 +1963,19 @@
       </c>
       <c r="D38" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>46286.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F38" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G38" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,5)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$O$5:$O$404,5),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -1984,27 +1984,27 @@
       </c>
       <c r="B39" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Cláudia Santos</v>
+        <v>Rodrigo Moreira</v>
       </c>
       <c r="C39" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Consulta</v>
+        <v>Teste ergométrico</v>
       </c>
       <c r="D39" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>46288.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F39" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="G39" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,6)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$O$5:$O$404,6),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B40" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Regina Duarte</v>
+        <v>Sérgio Martins</v>
       </c>
       <c r="C40" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D40" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F40" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G40" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,7)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$O$5:$O$404,7),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -2042,11 +2042,11 @@
       </c>
       <c r="B41" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$A$5:$A$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Rodrigo Moreira</v>
+        <v>Rafael Pereira</v>
       </c>
       <c r="C41" s="23" t="str">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$B$5:$B$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>Teste ergométrico</v>
+        <v>Avaliação endócrina</v>
       </c>
       <c r="D41" s="24">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$D$5:$D$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
@@ -2054,15 +2054,15 @@
       </c>
       <c r="E41" s="29">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$E$5:$E$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>46290.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F41" s="25">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$F$5:$F$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G41" s="30">
         <f>IFERROR(IF(LARGE(Parcelas!$O$5:$O$404,8)&gt;0,INDEX(Parcelas!$K$5:$K$404,MATCH(LARGE(Parcelas!$O$5:$O$404,8),Parcelas!$O$5:$O$404,0)),""),"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42"/>
@@ -2136,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2293,9 +2293,17 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Regra que vale mais que a régua: quem tem parcela vencida em aberto não combina novo pagamento a prazo. O próximo atendimento é à vista (Pix, dinheiro ou cartão) ou fica para depois de acertar o que está em atraso — sem constrangimento e em particular. No exemplo do kit, nenhum paciente com parcela vencida recebeu crédito novo, e o mesmo vale para orçamento aprovado a prazo (planilha 15).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -2507,19 +2515,19 @@
       </c>
       <c r="E8" s="25">
         <f>IF(A8="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A8,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>570</v>
+        <v>760</v>
       </c>
       <c r="F8" s="25">
         <f>IF(A8="","",D8-E8)</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G8" s="25">
         <f>IF(A8="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A8,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="H8" s="24" t="str">
         <f>IF(A8="","",IF(G8&gt;0,"Em atraso",IF(F8&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="9">
@@ -2535,7 +2543,7 @@
       </c>
       <c r="C9" s="24">
         <f>IF(A9="","",COUNTIFS(Parcelas!$A$5:$A$404,A9))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="25">
         <f>IF(A9="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A9))</f>
@@ -2543,19 +2551,19 @@
       </c>
       <c r="E9" s="25">
         <f>IF(A9="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A9,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="F9" s="25">
         <f>IF(A9="","",D9-E9)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="G9" s="25">
         <f>IF(A9="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A9,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="H9" s="24" t="str">
         <f>IF(A9="","",IF(G9&gt;0,"Em atraso",IF(F9&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="10">
@@ -2643,7 +2651,7 @@
       </c>
       <c r="C12" s="24">
         <f>IF(A12="","",COUNTIFS(Parcelas!$A$5:$A$404,A12))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="25">
         <f>IF(A12="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A12))</f>
@@ -2651,19 +2659,19 @@
       </c>
       <c r="E12" s="25">
         <f>IF(A12="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A12,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>760</v>
+        <v>380</v>
       </c>
       <c r="F12" s="25">
         <f>IF(A12="","",D12-E12)</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G12" s="25">
         <f>IF(A12="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A12,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H12" s="24" t="str">
         <f>IF(A12="","",IF(G12&gt;0,"Em atraso",IF(F12&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="13">
@@ -2715,7 +2723,7 @@
       </c>
       <c r="C14" s="24">
         <f>IF(A14="","",COUNTIFS(Parcelas!$A$5:$A$404,A14))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="25">
         <f>IF(A14="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A14))</f>
@@ -2723,19 +2731,19 @@
       </c>
       <c r="E14" s="25">
         <f>IF(A14="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A14,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="F14" s="25">
         <f>IF(A14="","",D14-E14)</f>
-        <v>1210</v>
+        <v>605</v>
       </c>
       <c r="G14" s="25">
         <f>IF(A14="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A14,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>830</v>
+        <v>0</v>
       </c>
       <c r="H14" s="24" t="str">
         <f>IF(A14="","",IF(G14&gt;0,"Em atraso",IF(F14&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Em dia</v>
       </c>
     </row>
     <row r="15">
@@ -2751,7 +2759,7 @@
       </c>
       <c r="C15" s="24">
         <f>IF(A15="","",COUNTIFS(Parcelas!$A$5:$A$404,A15))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25">
         <f>IF(A15="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A15))</f>
@@ -2787,15 +2795,15 @@
       </c>
       <c r="C16" s="24">
         <f>IF(A16="","",COUNTIFS(Parcelas!$A$5:$A$404,A16))</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="25">
         <f>IF(A16="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A16))</f>
-        <v>1580</v>
+        <v>1130</v>
       </c>
       <c r="E16" s="25">
         <f>IF(A16="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A16,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>1130</v>
+        <v>680</v>
       </c>
       <c r="F16" s="25">
         <f>IF(A16="","",D16-E16)</f>
@@ -2823,7 +2831,7 @@
       </c>
       <c r="C17" s="24">
         <f>IF(A17="","",COUNTIFS(Parcelas!$A$5:$A$404,A17))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="25">
         <f>IF(A17="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A17))</f>
@@ -2859,7 +2867,7 @@
       </c>
       <c r="C18" s="24">
         <f>IF(A18="","",COUNTIFS(Parcelas!$A$5:$A$404,A18))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25">
         <f>IF(A18="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A18))</f>
@@ -2867,11 +2875,11 @@
       </c>
       <c r="E18" s="25">
         <f>IF(A18="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A18,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="25">
         <f>IF(A18="","",D18-E18)</f>
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G18" s="25">
         <f>IF(A18="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A18,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -2895,7 +2903,7 @@
       </c>
       <c r="C19" s="24">
         <f>IF(A19="","",COUNTIFS(Parcelas!$A$5:$A$404,A19))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="25">
         <f>IF(A19="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A19))</f>
@@ -2967,7 +2975,7 @@
       </c>
       <c r="C21" s="24">
         <f>IF(A21="","",COUNTIFS(Parcelas!$A$5:$A$404,A21))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="25">
         <f>IF(A21="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A21))</f>
@@ -3003,15 +3011,15 @@
       </c>
       <c r="C22" s="24">
         <f>IF(A22="","",COUNTIFS(Parcelas!$A$5:$A$404,A22))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="25">
         <f>IF(A22="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A22))</f>
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E22" s="25">
         <f>IF(A22="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A22,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F22" s="25">
         <f>IF(A22="","",D22-E22)</f>
@@ -3039,7 +3047,7 @@
       </c>
       <c r="C23" s="24">
         <f>IF(A23="","",COUNTIFS(Parcelas!$A$5:$A$404,A23))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="25">
         <f>IF(A23="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A23))</f>
@@ -3111,7 +3119,7 @@
       </c>
       <c r="C25" s="24">
         <f>IF(A25="","",COUNTIFS(Parcelas!$A$5:$A$404,A25))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="25">
         <f>IF(A25="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A25))</f>
@@ -3119,19 +3127,19 @@
       </c>
       <c r="E25" s="25">
         <f>IF(A25="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A25,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="F25" s="25">
         <f>IF(A25="","",D25-E25)</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G25" s="25">
         <f>IF(A25="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A25,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="H25" s="24" t="str">
         <f>IF(A25="","",IF(G25&gt;0,"Em atraso",IF(F25&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="26">
@@ -3183,27 +3191,27 @@
       </c>
       <c r="C27" s="24">
         <f>IF(A27="","",COUNTIFS(Parcelas!$A$5:$A$404,A27))</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25">
         <f>IF(A27="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A27))</f>
-        <v>2280</v>
+        <v>1140</v>
       </c>
       <c r="E27" s="25">
         <f>IF(A27="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A27,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>2280</v>
+        <v>760</v>
       </c>
       <c r="F27" s="25">
         <f>IF(A27="","",D27-E27)</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="G27" s="25">
         <f>IF(A27="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A27,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H27" s="24" t="str">
         <f>IF(A27="","",IF(G27&gt;0,"Em atraso",IF(F27&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="28">
@@ -3291,7 +3299,7 @@
       </c>
       <c r="C30" s="24">
         <f>IF(A30="","",COUNTIFS(Parcelas!$A$5:$A$404,A30))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="25">
         <f>IF(A30="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A30))</f>
@@ -3299,11 +3307,11 @@
       </c>
       <c r="E30" s="25">
         <f>IF(A30="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A30,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="F30" s="25">
         <f>IF(A30="","",D30-E30)</f>
-        <v>950</v>
+        <v>760</v>
       </c>
       <c r="G30" s="25">
         <f>IF(A30="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A30,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -3327,7 +3335,7 @@
       </c>
       <c r="C31" s="24">
         <f>IF(A31="","",COUNTIFS(Parcelas!$A$5:$A$404,A31))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25">
         <f>IF(A31="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A31))</f>
@@ -3515,19 +3523,19 @@
       </c>
       <c r="E36" s="25">
         <f>IF(A36="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A36,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>1440</v>
+        <v>680</v>
       </c>
       <c r="F36" s="25">
         <f>IF(A36="","",D36-E36)</f>
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="G36" s="25">
         <f>IF(A36="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A36,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="H36" s="24" t="str">
         <f>IF(A36="","",IF(G36&gt;0,"Em atraso",IF(F36&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="37">
@@ -3551,19 +3559,19 @@
       </c>
       <c r="E37" s="25">
         <f>IF(A37="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A37,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F37" s="25">
         <f>IF(A37="","",D37-E37)</f>
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G37" s="25">
         <f>IF(A37="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A37,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H37" s="24" t="str">
         <f>IF(A37="","",IF(G37&gt;0,"Em atraso",IF(F37&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Em dia</v>
       </c>
     </row>
     <row r="38">
@@ -3579,19 +3587,19 @@
       </c>
       <c r="C38" s="24">
         <f>IF(A38="","",COUNTIFS(Parcelas!$A$5:$A$404,A38))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D38" s="25">
         <f>IF(A38="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A38))</f>
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="E38" s="25">
         <f>IF(A38="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A38,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F38" s="25">
         <f>IF(A38="","",D38-E38)</f>
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G38" s="25">
         <f>IF(A38="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A38,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -3687,7 +3695,7 @@
       </c>
       <c r="C41" s="24">
         <f>IF(A41="","",COUNTIFS(Parcelas!$A$5:$A$404,A41))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="25">
         <f>IF(A41="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A41))</f>
@@ -3731,19 +3739,19 @@
       </c>
       <c r="E42" s="25">
         <f>IF(A42="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A42,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>950</v>
+        <v>1140</v>
       </c>
       <c r="F42" s="25">
         <f>IF(A42="","",D42-E42)</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G42" s="25">
         <f>IF(A42="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A42,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="H42" s="24" t="str">
         <f>IF(A42="","",IF(G42&gt;0,"Em atraso",IF(F42&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="43">
@@ -3767,19 +3775,19 @@
       </c>
       <c r="E43" s="25">
         <f>IF(A43="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A43,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>1180</v>
+        <v>1480</v>
       </c>
       <c r="F43" s="25">
         <f>IF(A43="","",D43-E43)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G43" s="25">
         <f>IF(A43="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A43,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H43" s="24" t="str">
         <f>IF(A43="","",IF(G43&gt;0,"Em atraso",IF(F43&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="44">
@@ -3795,7 +3803,7 @@
       </c>
       <c r="C44" s="24">
         <f>IF(A44="","",COUNTIFS(Parcelas!$A$5:$A$404,A44))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="25">
         <f>IF(A44="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A44))</f>
@@ -3831,7 +3839,7 @@
       </c>
       <c r="C45" s="24">
         <f>IF(A45="","",COUNTIFS(Parcelas!$A$5:$A$404,A45))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" s="25">
         <f>IF(A45="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A45))</f>
@@ -3839,19 +3847,19 @@
       </c>
       <c r="E45" s="25">
         <f>IF(A45="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A45,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>760</v>
+        <v>570</v>
       </c>
       <c r="F45" s="25">
         <f>IF(A45="","",D45-E45)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="G45" s="25">
         <f>IF(A45="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A45,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="H45" s="24" t="str">
         <f>IF(A45="","",IF(G45&gt;0,"Em atraso",IF(F45&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="46">
@@ -3867,7 +3875,7 @@
       </c>
       <c r="C46" s="24">
         <f>IF(A46="","",COUNTIFS(Parcelas!$A$5:$A$404,A46))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" s="25">
         <f>IF(A46="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A46))</f>
@@ -3911,15 +3919,15 @@
       </c>
       <c r="E47" s="25">
         <f>IF(A47="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A47,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>190</v>
+        <v>570</v>
       </c>
       <c r="F47" s="25">
         <f>IF(A47="","",D47-E47)</f>
-        <v>570</v>
+        <v>190</v>
       </c>
       <c r="G47" s="25">
         <f>IF(A47="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A47,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>570</v>
+        <v>190</v>
       </c>
       <c r="H47" s="24" t="str">
         <f>IF(A47="","",IF(G47&gt;0,"Em atraso",IF(F47&gt;0,"Em dia","Sem parcela em aberto")))</f>
@@ -3939,7 +3947,7 @@
       </c>
       <c r="C48" s="24">
         <f>IF(A48="","",COUNTIFS(Parcelas!$A$5:$A$404,A48))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="25">
         <f>IF(A48="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A48))</f>
@@ -3947,19 +3955,19 @@
       </c>
       <c r="E48" s="25">
         <f>IF(A48="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A48,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F48" s="25">
         <f>IF(A48="","",D48-E48)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G48" s="25">
         <f>IF(A48="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A48,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H48" s="24" t="str">
         <f>IF(A48="","",IF(G48&gt;0,"Em atraso",IF(F48&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="49">
@@ -3975,7 +3983,7 @@
       </c>
       <c r="C49" s="24">
         <f>IF(A49="","",COUNTIFS(Parcelas!$A$5:$A$404,A49))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="25">
         <f>IF(A49="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A49))</f>
@@ -3983,19 +3991,19 @@
       </c>
       <c r="E49" s="25">
         <f>IF(A49="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A49,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="F49" s="25">
         <f>IF(A49="","",D49-E49)</f>
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G49" s="25">
         <f>IF(A49="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A49,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H49" s="24" t="str">
         <f>IF(A49="","",IF(G49&gt;0,"Em atraso",IF(F49&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em dia</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="50">
@@ -4047,27 +4055,27 @@
       </c>
       <c r="C51" s="24">
         <f>IF(A51="","",COUNTIFS(Parcelas!$A$5:$A$404,A51))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="25">
         <f>IF(A51="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A51))</f>
-        <v>1140</v>
+        <v>760</v>
       </c>
       <c r="E51" s="25">
         <f>IF(A51="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A51,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>1140</v>
+        <v>570</v>
       </c>
       <c r="F51" s="25">
         <f>IF(A51="","",D51-E51)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="G51" s="25">
         <f>IF(A51="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A51,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="H51" s="24" t="str">
         <f>IF(A51="","",IF(G51&gt;0,"Em atraso",IF(F51&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em atraso</v>
       </c>
     </row>
     <row r="52">
@@ -4083,7 +4091,7 @@
       </c>
       <c r="C52" s="24">
         <f>IF(A52="","",COUNTIFS(Parcelas!$A$5:$A$404,A52))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25">
         <f>IF(A52="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A52))</f>
@@ -4091,11 +4099,11 @@
       </c>
       <c r="E52" s="25">
         <f>IF(A52="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A52,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F52" s="25">
         <f>IF(A52="","",D52-E52)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G52" s="25">
         <f>IF(A52="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A52,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -4103,7 +4111,7 @@
       </c>
       <c r="H52" s="24" t="str">
         <f>IF(A52="","",IF(G52&gt;0,"Em atraso",IF(F52&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Sem parcela em aberto</v>
+        <v>Em dia</v>
       </c>
     </row>
     <row r="53">
@@ -4119,7 +4127,7 @@
       </c>
       <c r="C53" s="24">
         <f>IF(A53="","",COUNTIFS(Parcelas!$A$5:$A$404,A53))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="25">
         <f>IF(A53="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A53))</f>
@@ -4127,11 +4135,11 @@
       </c>
       <c r="E53" s="25">
         <f>IF(A53="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A53,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="F53" s="25">
         <f>IF(A53="","",D53-E53)</f>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G53" s="25">
         <f>IF(A53="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A53,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -4139,7 +4147,7 @@
       </c>
       <c r="H53" s="24" t="str">
         <f>IF(A53="","",IF(G53&gt;0,"Em atraso",IF(F53&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em dia</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="54">
@@ -4155,7 +4163,7 @@
       </c>
       <c r="C54" s="24">
         <f>IF(A54="","",COUNTIFS(Parcelas!$A$5:$A$404,A54))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="25">
         <f>IF(A54="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A54))</f>
@@ -4191,7 +4199,7 @@
       </c>
       <c r="C55" s="24">
         <f>IF(A55="","",COUNTIFS(Parcelas!$A$5:$A$404,A55))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D55" s="25">
         <f>IF(A55="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A55))</f>
@@ -4199,19 +4207,19 @@
       </c>
       <c r="E55" s="25">
         <f>IF(A55="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A55,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>760</v>
+        <v>1140</v>
       </c>
       <c r="F55" s="25">
         <f>IF(A55="","",D55-E55)</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G55" s="25">
         <f>IF(A55="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A55,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H55" s="24" t="str">
         <f>IF(A55="","",IF(G55&gt;0,"Em atraso",IF(F55&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="56">
@@ -4227,7 +4235,7 @@
       </c>
       <c r="C56" s="24">
         <f>IF(A56="","",COUNTIFS(Parcelas!$A$5:$A$404,A56))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="25">
         <f>IF(A56="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A56))</f>
@@ -4307,19 +4315,19 @@
       </c>
       <c r="E58" s="25">
         <f>IF(A58="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A58,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F58" s="25">
         <f>IF(A58="","",D58-E58)</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G58" s="25">
         <f>IF(A58="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A58,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H58" s="24" t="str">
         <f>IF(A58="","",IF(G58&gt;0,"Em atraso",IF(F58&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="59">
@@ -4335,7 +4343,7 @@
       </c>
       <c r="C59" s="24">
         <f>IF(A59="","",COUNTIFS(Parcelas!$A$5:$A$404,A59))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" s="25">
         <f>IF(A59="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A59))</f>
@@ -4371,7 +4379,7 @@
       </c>
       <c r="C60" s="24">
         <f>IF(A60="","",COUNTIFS(Parcelas!$A$5:$A$404,A60))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="25">
         <f>IF(A60="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A60))</f>
@@ -4379,11 +4387,11 @@
       </c>
       <c r="E60" s="25">
         <f>IF(A60="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A60,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="F60" s="25">
         <f>IF(A60="","",D60-E60)</f>
-        <v>380</v>
+        <v>570</v>
       </c>
       <c r="G60" s="25">
         <f>IF(A60="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A60,Parcelas!$I$5:$I$404,"Vencida"))</f>
@@ -4407,7 +4415,7 @@
       </c>
       <c r="C61" s="24">
         <f>IF(A61="","",COUNTIFS(Parcelas!$A$5:$A$404,A61))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="25">
         <f>IF(A61="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A61))</f>
@@ -4443,7 +4451,7 @@
       </c>
       <c r="C62" s="24">
         <f>IF(A62="","",COUNTIFS(Parcelas!$A$5:$A$404,A62))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" s="25">
         <f>IF(A62="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A62))</f>
@@ -4451,19 +4459,19 @@
       </c>
       <c r="E62" s="25">
         <f>IF(A62="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A62,Parcelas!$I$5:$I$404,"Paga"))</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="F62" s="25">
         <f>IF(A62="","",D62-E62)</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G62" s="25">
         <f>IF(A62="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A62,Parcelas!$I$5:$I$404,"Vencida"))</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="H62" s="24" t="str">
         <f>IF(A62="","",IF(G62&gt;0,"Em atraso",IF(F62&gt;0,"Em dia","Sem parcela em aberto")))</f>
-        <v>Em atraso</v>
+        <v>Sem parcela em aberto</v>
       </c>
     </row>
     <row r="63">
@@ -4515,7 +4523,7 @@
       </c>
       <c r="C64" s="24">
         <f>IF(A64="","",COUNTIFS(Parcelas!$A$5:$A$404,A64))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" s="25">
         <f>IF(A64="","",SUMIFS(Parcelas!$F$5:$F$404,Parcelas!$A$5:$A$404,A64))</f>
@@ -14790,12 +14798,12 @@
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Reis</t>
+          <t>Carlos Oliveira</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C15" s="37" t="n">
@@ -14808,7 +14816,7 @@
         <v>46074</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G15" s="35" t="inlineStr">
         <is>
@@ -14816,7 +14824,7 @@
         </is>
       </c>
       <c r="H15" s="37" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="I15" s="24" t="str">
         <f>IF(A15="","",IF(G15="Sim","Paga",IF(E15="","Sem vencimento",IF(E15&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -14862,10 +14870,10 @@
         <v>46044</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="37" t="n">
-        <v>46074</v>
+        <v>46104</v>
       </c>
       <c r="F16" s="38" t="n">
         <v>190</v>
@@ -14876,7 +14884,7 @@
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="I16" s="24" t="str">
         <f>IF(A16="","",IF(G16="Sim","Paga",IF(E16="","Sem vencimento",IF(E16&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -14910,25 +14918,25 @@
     <row r="17">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>Carlos Oliveira</t>
+          <t>Gabriel Reis</t>
         </is>
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C17" s="37" t="n">
         <v>46044</v>
       </c>
       <c r="D17" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="37" t="n">
-        <v>46104</v>
+        <v>46074</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
@@ -14936,7 +14944,7 @@
         </is>
       </c>
       <c r="H17" s="37" t="n">
-        <v>46104</v>
+        <v>46074</v>
       </c>
       <c r="I17" s="24" t="str">
         <f>IF(A17="","",IF(G17="Sim","Paga",IF(E17="","Sem vencimento",IF(E17&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16408,25 +16416,25 @@
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Fernanda Freitas</t>
+          <t>Natália Martins</t>
         </is>
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C42" s="37" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="D42" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="37" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="F42" s="38" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="G42" s="35" t="inlineStr">
         <is>
@@ -16434,7 +16442,7 @@
         </is>
       </c>
       <c r="H42" s="37" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="I42" s="24" t="str">
         <f>IF(A42="","",IF(G42="Sim","Paga",IF(E42="","Sem vencimento",IF(E42&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16468,25 +16476,25 @@
     <row r="43">
       <c r="A43" s="33" t="inlineStr">
         <is>
-          <t>Fernanda Freitas</t>
+          <t>Natália Martins</t>
         </is>
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C43" s="37" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="D43" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E43" s="37" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="F43" s="38" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="G43" s="35" t="inlineStr">
         <is>
@@ -16494,7 +16502,7 @@
         </is>
       </c>
       <c r="H43" s="37" t="n">
-        <v>46156</v>
+        <v>46159</v>
       </c>
       <c r="I43" s="24" t="str">
         <f>IF(A43="","",IF(G43="Sim","Paga",IF(E43="","Sem vencimento",IF(E43&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16528,7 +16536,7 @@
     <row r="44">
       <c r="A44" s="33" t="inlineStr">
         <is>
-          <t>Natália Martins</t>
+          <t>Otávio Cardoso</t>
         </is>
       </c>
       <c r="B44" s="33" t="inlineStr">
@@ -16537,13 +16545,13 @@
         </is>
       </c>
       <c r="C44" s="37" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="D44" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E44" s="37" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="F44" s="38" t="n">
         <v>380</v>
@@ -16554,7 +16562,7 @@
         </is>
       </c>
       <c r="H44" s="37" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="I44" s="24" t="str">
         <f>IF(A44="","",IF(G44="Sim","Paga",IF(E44="","Sem vencimento",IF(E44&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16588,7 +16596,7 @@
     <row r="45">
       <c r="A45" s="33" t="inlineStr">
         <is>
-          <t>Otávio Cardoso</t>
+          <t>Patrícia Fernandes</t>
         </is>
       </c>
       <c r="B45" s="33" t="inlineStr">
@@ -16597,13 +16605,13 @@
         </is>
       </c>
       <c r="C45" s="37" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="D45" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E45" s="37" t="n">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="F45" s="38" t="n">
         <v>190</v>
@@ -16614,7 +16622,7 @@
         </is>
       </c>
       <c r="H45" s="37" t="n">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="I45" s="24" t="str">
         <f>IF(A45="","",IF(G45="Sim","Paga",IF(E45="","Sem vencimento",IF(E45&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16648,7 +16656,7 @@
     <row r="46">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>Otávio Cardoso</t>
+          <t>Patrícia Fernandes</t>
         </is>
       </c>
       <c r="B46" s="33" t="inlineStr">
@@ -16657,14 +16665,14 @@
         </is>
       </c>
       <c r="C46" s="37" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="D46" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E46" s="37">
-        <f>TODAY()-121</f>
-        <v>46158.0</v>
+        <f>TODAY()-119</f>
+        <v>46160.0</v>
       </c>
       <c r="F46" s="38" t="n">
         <v>190</v>
@@ -16681,7 +16689,7 @@
       </c>
       <c r="J46" s="30">
         <f>IF(I46="Vencida",Config!$B$5-E46,"")</f>
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K46" s="30">
         <f>IF(I46="A vencer",E46-Config!$B$5,"")</f>
@@ -16697,7 +16705,7 @@
       </c>
       <c r="N46" s="39">
         <f>IF(I46="Vencida",F46*J46+ROW()/100000,0)</f>
-        <v>22990.00046</v>
+        <v>22610.00046</v>
       </c>
       <c r="O46" s="39">
         <f>IF(AND(I46="A vencer",K46&lt;=Config!$B$7),100000-K46-ROW()/100000,0)</f>
@@ -16707,7 +16715,7 @@
     <row r="47">
       <c r="A47" s="33" t="inlineStr">
         <is>
-          <t>Patrícia Fernandes</t>
+          <t>Camila Freitas</t>
         </is>
       </c>
       <c r="B47" s="33" t="inlineStr">
@@ -16716,13 +16724,13 @@
         </is>
       </c>
       <c r="C47" s="37" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="D47" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="37" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="F47" s="38" t="n">
         <v>380</v>
@@ -16733,7 +16741,7 @@
         </is>
       </c>
       <c r="H47" s="37" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="I47" s="24" t="str">
         <f>IF(A47="","",IF(G47="Sim","Paga",IF(E47="","Sem vencimento",IF(E47&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16767,7 +16775,7 @@
     <row r="48">
       <c r="A48" s="33" t="inlineStr">
         <is>
-          <t>Camila Freitas</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="B48" s="33" t="inlineStr">
@@ -16776,13 +16784,13 @@
         </is>
       </c>
       <c r="C48" s="37" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="D48" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="37" t="n">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="F48" s="38" t="n">
         <v>190</v>
@@ -16793,7 +16801,7 @@
         </is>
       </c>
       <c r="H48" s="37" t="n">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="I48" s="24" t="str">
         <f>IF(A48="","",IF(G48="Sim","Paga",IF(E48="","Sem vencimento",IF(E48&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16827,7 +16835,7 @@
     <row r="49">
       <c r="A49" s="33" t="inlineStr">
         <is>
-          <t>Camila Freitas</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="B49" s="33" t="inlineStr">
@@ -16836,14 +16844,14 @@
         </is>
       </c>
       <c r="C49" s="37" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="D49" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E49" s="37">
-        <f>TODAY()-118</f>
-        <v>46161.0</v>
+        <f>TODAY()-114</f>
+        <v>46165.0</v>
       </c>
       <c r="F49" s="38" t="n">
         <v>190</v>
@@ -16860,7 +16868,7 @@
       </c>
       <c r="J49" s="30">
         <f>IF(I49="Vencida",Config!$B$5-E49,"")</f>
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K49" s="30">
         <f>IF(I49="A vencer",E49-Config!$B$5,"")</f>
@@ -16876,7 +16884,7 @@
       </c>
       <c r="N49" s="39">
         <f>IF(I49="Vencida",F49*J49+ROW()/100000,0)</f>
-        <v>22420.00049</v>
+        <v>21660.00049</v>
       </c>
       <c r="O49" s="39">
         <f>IF(AND(I49="A vencer",K49&lt;=Config!$B$7),100000-K49-ROW()/100000,0)</f>
@@ -16886,7 +16894,7 @@
     <row r="50">
       <c r="A50" s="33" t="inlineStr">
         <is>
-          <t>Rafael Dias</t>
+          <t>Renato Dias</t>
         </is>
       </c>
       <c r="B50" s="33" t="inlineStr">
@@ -16895,13 +16903,13 @@
         </is>
       </c>
       <c r="C50" s="37" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="D50" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="37" t="n">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="F50" s="38" t="n">
         <v>380</v>
@@ -16912,7 +16920,7 @@
         </is>
       </c>
       <c r="H50" s="37" t="n">
-        <v>46135</v>
+        <v>46137</v>
       </c>
       <c r="I50" s="24" t="str">
         <f>IF(A50="","",IF(G50="Sim","Paga",IF(E50="","Sem vencimento",IF(E50&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -16946,7 +16954,7 @@
     <row r="51">
       <c r="A51" s="33" t="inlineStr">
         <is>
-          <t>Renato Dias</t>
+          <t>Fábio Correia</t>
         </is>
       </c>
       <c r="B51" s="33" t="inlineStr">
@@ -16955,13 +16963,13 @@
         </is>
       </c>
       <c r="C51" s="37" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="D51" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="37" t="n">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F51" s="38" t="n">
         <v>380</v>
@@ -16972,7 +16980,7 @@
         </is>
       </c>
       <c r="H51" s="37" t="n">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="I51" s="24" t="str">
         <f>IF(A51="","",IF(G51="Sim","Paga",IF(E51="","Sem vencimento",IF(E51&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17006,7 +17014,7 @@
     <row r="52">
       <c r="A52" s="33" t="inlineStr">
         <is>
-          <t>Fábio Correia</t>
+          <t>Regina Teixeira</t>
         </is>
       </c>
       <c r="B52" s="33" t="inlineStr">
@@ -17015,13 +17023,13 @@
         </is>
       </c>
       <c r="C52" s="37" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="D52" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E52" s="37" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="F52" s="38" t="n">
         <v>190</v>
@@ -17032,7 +17040,7 @@
         </is>
       </c>
       <c r="H52" s="37" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="I52" s="24" t="str">
         <f>IF(A52="","",IF(G52="Sim","Paga",IF(E52="","Sem vencimento",IF(E52&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17066,7 +17074,7 @@
     <row r="53">
       <c r="A53" s="33" t="inlineStr">
         <is>
-          <t>Fábio Correia</t>
+          <t>Regina Teixeira</t>
         </is>
       </c>
       <c r="B53" s="33" t="inlineStr">
@@ -17075,13 +17083,13 @@
         </is>
       </c>
       <c r="C53" s="37" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="D53" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E53" s="37" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F53" s="38" t="n">
         <v>190</v>
@@ -17092,7 +17100,7 @@
         </is>
       </c>
       <c r="H53" s="37" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="I53" s="24" t="str">
         <f>IF(A53="","",IF(G53="Sim","Paga",IF(E53="","Sem vencimento",IF(E53&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17126,7 +17134,7 @@
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t>Regina Teixeira</t>
+          <t>Gabriel Fernandes</t>
         </is>
       </c>
       <c r="B54" s="33" t="inlineStr">
@@ -17135,13 +17143,13 @@
         </is>
       </c>
       <c r="C54" s="37" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="D54" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="37" t="n">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="F54" s="38" t="n">
         <v>380</v>
@@ -17152,7 +17160,7 @@
         </is>
       </c>
       <c r="H54" s="37" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="I54" s="24" t="str">
         <f>IF(A54="","",IF(G54="Sim","Paga",IF(E54="","Sem vencimento",IF(E54&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17186,7 +17194,7 @@
     <row r="55">
       <c r="A55" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Fernandes</t>
+          <t>Gisele Xavier</t>
         </is>
       </c>
       <c r="B55" s="33" t="inlineStr">
@@ -17195,13 +17203,13 @@
         </is>
       </c>
       <c r="C55" s="37" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="D55" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="37" t="n">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="F55" s="38" t="n">
         <v>380</v>
@@ -17212,7 +17220,7 @@
         </is>
       </c>
       <c r="H55" s="37" t="n">
-        <v>46144</v>
+        <v>46148</v>
       </c>
       <c r="I55" s="24" t="str">
         <f>IF(A55="","",IF(G55="Sim","Paga",IF(E55="","Sem vencimento",IF(E55&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17246,12 +17254,12 @@
     <row r="56">
       <c r="A56" s="33" t="inlineStr">
         <is>
-          <t>Gisele Xavier</t>
+          <t>Marcelo Santos</t>
         </is>
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="C56" s="37" t="n">
@@ -17264,7 +17272,7 @@
         <v>46148</v>
       </c>
       <c r="F56" s="38" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="G56" s="35" t="inlineStr">
         <is>
@@ -17272,7 +17280,7 @@
         </is>
       </c>
       <c r="H56" s="37" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="I56" s="24" t="str">
         <f>IF(A56="","",IF(G56="Sim","Paga",IF(E56="","Sem vencimento",IF(E56&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17332,7 +17340,7 @@
         </is>
       </c>
       <c r="H57" s="37" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="I57" s="24" t="str">
         <f>IF(A57="","",IF(G57="Sim","Paga",IF(E57="","Sem vencimento",IF(E57&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17366,57 +17374,56 @@
     <row r="58">
       <c r="A58" s="33" t="inlineStr">
         <is>
-          <t>Marcelo Santos</t>
+          <t>Priscila Reis</t>
         </is>
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C58" s="37" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="D58" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="37" t="n">
-        <v>46148</v>
+      <c r="E58" s="37">
+        <f>TODAY()-130</f>
+        <v>46149.0</v>
       </c>
       <c r="F58" s="38" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G58" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H58" s="37" t="n">
-        <v>46148</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H58" s="37" t="n"/>
       <c r="I58" s="24" t="str">
         <f>IF(A58="","",IF(G58="Sim","Paga",IF(E58="","Sem vencimento",IF(E58&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J58" s="30">
         <f>IF(I58="Vencida",Config!$B$5-E58,"")</f>
-        <v/>
+        <v>130</v>
       </c>
       <c r="K58" s="30">
         <f>IF(I58="A vencer",E58-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L58" s="24">
+      <c r="L58" s="24" t="str">
         <f>IF(I58&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J58)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J58))))</f>
-        <v/>
-      </c>
-      <c r="M58" s="23">
+        <v>30 dias ou mais</v>
+      </c>
+      <c r="M58" s="23" t="str">
         <f>IF(I58&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J58)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J58))))</f>
-        <v/>
+        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
       </c>
       <c r="N58" s="39">
         <f>IF(I58="Vencida",F58*J58+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>52000.00058</v>
       </c>
       <c r="O58" s="39">
         <f>IF(AND(I58="A vencer",K58&lt;=Config!$B$7),100000-K58-ROW()/100000,0)</f>
@@ -17440,42 +17447,43 @@
       <c r="D59" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="37">
-        <f>TODAY()-130</f>
-        <v>46149.0</v>
+      <c r="E59" s="37" t="n">
+        <v>46149</v>
       </c>
       <c r="F59" s="38" t="n">
         <v>380</v>
       </c>
       <c r="G59" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H59" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H59" s="37" t="n">
+        <v>46149</v>
+      </c>
       <c r="I59" s="24" t="str">
         <f>IF(A59="","",IF(G59="Sim","Paga",IF(E59="","Sem vencimento",IF(E59&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J59" s="30">
         <f>IF(I59="Vencida",Config!$B$5-E59,"")</f>
-        <v>130</v>
+        <v/>
       </c>
       <c r="K59" s="30">
         <f>IF(I59="A vencer",E59-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L59" s="24" t="str">
+      <c r="L59" s="24">
         <f>IF(I59&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J59)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J59))))</f>
-        <v>30 dias ou mais</v>
-      </c>
-      <c r="M59" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M59" s="23">
         <f>IF(I59&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J59)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J59))))</f>
-        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
+        <v/>
       </c>
       <c r="N59" s="39">
         <f>IF(I59="Vencida",F59*J59+ROW()/100000,0)</f>
-        <v>49400.00059</v>
+        <v>0</v>
       </c>
       <c r="O59" s="39">
         <f>IF(AND(I59="A vencer",K59&lt;=Config!$B$7),100000-K59-ROW()/100000,0)</f>
@@ -17485,25 +17493,25 @@
     <row r="60">
       <c r="A60" s="33" t="inlineStr">
         <is>
-          <t>Priscila Reis</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C60" s="37" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="D60" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E60" s="37" t="n">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="F60" s="38" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G60" s="35" t="inlineStr">
         <is>
@@ -17511,7 +17519,7 @@
         </is>
       </c>
       <c r="H60" s="37" t="n">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="I60" s="24" t="str">
         <f>IF(A60="","",IF(G60="Sim","Paga",IF(E60="","Sem vencimento",IF(E60&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17545,25 +17553,25 @@
     <row r="61">
       <c r="A61" s="33" t="inlineStr">
         <is>
-          <t>Priscila Reis</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C61" s="37" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="D61" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E61" s="37" t="n">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="F61" s="38" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G61" s="35" t="inlineStr">
         <is>
@@ -17571,7 +17579,7 @@
         </is>
       </c>
       <c r="H61" s="37" t="n">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="I61" s="24" t="str">
         <f>IF(A61="","",IF(G61="Sim","Paga",IF(E61="","Sem vencimento",IF(E61&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17605,25 +17613,25 @@
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C62" s="37" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="D62" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="37" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="F62" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G62" s="35" t="inlineStr">
         <is>
@@ -17631,7 +17639,7 @@
         </is>
       </c>
       <c r="H62" s="37" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="I62" s="24" t="str">
         <f>IF(A62="","",IF(G62="Sim","Paga",IF(E62="","Sem vencimento",IF(E62&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17665,25 +17673,25 @@
     <row r="63">
       <c r="A63" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C63" s="37" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="D63" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E63" s="37" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="F63" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G63" s="35" t="inlineStr">
         <is>
@@ -17691,7 +17699,7 @@
         </is>
       </c>
       <c r="H63" s="37" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="I63" s="24" t="str">
         <f>IF(A63="","",IF(G63="Sim","Paga",IF(E63="","Sem vencimento",IF(E63&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17725,25 +17733,25 @@
     <row r="64">
       <c r="A64" s="33" t="inlineStr">
         <is>
-          <t>Larissa Costa</t>
+          <t>Camila Dias</t>
         </is>
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C64" s="37" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="D64" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="37" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F64" s="38" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="G64" s="35" t="inlineStr">
         <is>
@@ -17751,7 +17759,7 @@
         </is>
       </c>
       <c r="H64" s="37" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="I64" s="24" t="str">
         <f>IF(A64="","",IF(G64="Sim","Paga",IF(E64="","Sem vencimento",IF(E64&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17785,7 +17793,7 @@
     <row r="65">
       <c r="A65" s="33" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Camila Dias</t>
         </is>
       </c>
       <c r="B65" s="33" t="inlineStr">
@@ -17797,10 +17805,10 @@
         <v>46126</v>
       </c>
       <c r="D65" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="37" t="n">
-        <v>46156</v>
+        <v>46186</v>
       </c>
       <c r="F65" s="38" t="n">
         <v>200</v>
@@ -17811,7 +17819,7 @@
         </is>
       </c>
       <c r="H65" s="37" t="n">
-        <v>46157</v>
+        <v>46186</v>
       </c>
       <c r="I65" s="24" t="str">
         <f>IF(A65="","",IF(G65="Sim","Paga",IF(E65="","Sem vencimento",IF(E65&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17845,7 +17853,7 @@
     <row r="66">
       <c r="A66" s="33" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Carlos Freitas</t>
         </is>
       </c>
       <c r="B66" s="33" t="inlineStr">
@@ -17857,10 +17865,10 @@
         <v>46126</v>
       </c>
       <c r="D66" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="37" t="n">
-        <v>46186</v>
+        <v>46156</v>
       </c>
       <c r="F66" s="38" t="n">
         <v>200</v>
@@ -17871,7 +17879,7 @@
         </is>
       </c>
       <c r="H66" s="37" t="n">
-        <v>46186</v>
+        <v>46157</v>
       </c>
       <c r="I66" s="24" t="str">
         <f>IF(A66="","",IF(G66="Sim","Paga",IF(E66="","Sem vencimento",IF(E66&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17905,7 +17913,7 @@
     <row r="67">
       <c r="A67" s="33" t="inlineStr">
         <is>
-          <t>Camila Dias</t>
+          <t>Carlos Freitas</t>
         </is>
       </c>
       <c r="B67" s="33" t="inlineStr">
@@ -17917,10 +17925,10 @@
         <v>46126</v>
       </c>
       <c r="D67" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="37" t="n">
-        <v>46156</v>
+        <v>46186</v>
       </c>
       <c r="F67" s="38" t="n">
         <v>200</v>
@@ -17931,7 +17939,7 @@
         </is>
       </c>
       <c r="H67" s="37" t="n">
-        <v>46157</v>
+        <v>46187</v>
       </c>
       <c r="I67" s="24" t="str">
         <f>IF(A67="","",IF(G67="Sim","Paga",IF(E67="","Sem vencimento",IF(E67&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -17965,7 +17973,7 @@
     <row r="68">
       <c r="A68" s="33" t="inlineStr">
         <is>
-          <t>Camila Dias</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="B68" s="33" t="inlineStr">
@@ -17977,13 +17985,13 @@
         <v>46126</v>
       </c>
       <c r="D68" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="37" t="n">
-        <v>46186</v>
+        <v>46156</v>
       </c>
       <c r="F68" s="38" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
@@ -17991,7 +17999,7 @@
         </is>
       </c>
       <c r="H68" s="37" t="n">
-        <v>46187</v>
+        <v>46157</v>
       </c>
       <c r="I68" s="24" t="str">
         <f>IF(A68="","",IF(G68="Sim","Paga",IF(E68="","Sem vencimento",IF(E68&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18025,25 +18033,25 @@
     <row r="69">
       <c r="A69" s="33" t="inlineStr">
         <is>
-          <t>Carlos Freitas</t>
+          <t>Patrícia Fernandes</t>
         </is>
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C69" s="37" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="D69" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="37" t="n">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="F69" s="38" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G69" s="35" t="inlineStr">
         <is>
@@ -18051,7 +18059,7 @@
         </is>
       </c>
       <c r="H69" s="37" t="n">
-        <v>46159</v>
+        <v>46165</v>
       </c>
       <c r="I69" s="24" t="str">
         <f>IF(A69="","",IF(G69="Sim","Paga",IF(E69="","Sem vencimento",IF(E69&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18085,25 +18093,25 @@
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>Carlos Freitas</t>
+          <t>Patrícia Fernandes</t>
         </is>
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C70" s="37" t="n">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="D70" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E70" s="37" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="F70" s="38" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G70" s="35" t="inlineStr">
         <is>
@@ -18111,7 +18119,7 @@
         </is>
       </c>
       <c r="H70" s="37" t="n">
-        <v>46186</v>
+        <v>46192</v>
       </c>
       <c r="I70" s="24" t="str">
         <f>IF(A70="","",IF(G70="Sim","Paga",IF(E70="","Sem vencimento",IF(E70&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18145,25 +18153,25 @@
     <row r="71">
       <c r="A71" s="33" t="inlineStr">
         <is>
-          <t>Patrícia Fernandes</t>
+          <t>Fábio Gomes</t>
         </is>
       </c>
       <c r="B71" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C71" s="37" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="D71" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E71" s="37" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="F71" s="38" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="G71" s="35" t="inlineStr">
         <is>
@@ -18171,7 +18179,7 @@
         </is>
       </c>
       <c r="H71" s="37" t="n">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="I71" s="24" t="str">
         <f>IF(A71="","",IF(G71="Sim","Paga",IF(E71="","Sem vencimento",IF(E71&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18205,25 +18213,25 @@
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>Fábio Gomes</t>
+          <t>Henrique Ribeiro</t>
         </is>
       </c>
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C72" s="37" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="D72" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E72" s="37" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F72" s="38" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G72" s="35" t="inlineStr">
         <is>
@@ -18231,7 +18239,7 @@
         </is>
       </c>
       <c r="H72" s="37" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="I72" s="24" t="str">
         <f>IF(A72="","",IF(G72="Sim","Paga",IF(E72="","Sem vencimento",IF(E72&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18265,7 +18273,7 @@
     <row r="73">
       <c r="A73" s="33" t="inlineStr">
         <is>
-          <t>Henrique Ribeiro</t>
+          <t>Otávio Cardoso</t>
         </is>
       </c>
       <c r="B73" s="33" t="inlineStr">
@@ -18274,13 +18282,13 @@
         </is>
       </c>
       <c r="C73" s="37" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="D73" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E73" s="37" t="n">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="F73" s="38" t="n">
         <v>380</v>
@@ -18291,7 +18299,7 @@
         </is>
       </c>
       <c r="H73" s="37" t="n">
-        <v>46166</v>
+        <v>46169</v>
       </c>
       <c r="I73" s="24" t="str">
         <f>IF(A73="","",IF(G73="Sim","Paga",IF(E73="","Sem vencimento",IF(E73&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18325,7 +18333,7 @@
     <row r="74">
       <c r="A74" s="33" t="inlineStr">
         <is>
-          <t>Otávio Cardoso</t>
+          <t>Rafael Barros</t>
         </is>
       </c>
       <c r="B74" s="33" t="inlineStr">
@@ -18334,13 +18342,13 @@
         </is>
       </c>
       <c r="C74" s="37" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D74" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E74" s="37" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F74" s="38" t="n">
         <v>380</v>
@@ -18351,7 +18359,7 @@
         </is>
       </c>
       <c r="H74" s="37" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="I74" s="24" t="str">
         <f>IF(A74="","",IF(G74="Sim","Paga",IF(E74="","Sem vencimento",IF(E74&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18385,7 +18393,7 @@
     <row r="75">
       <c r="A75" s="33" t="inlineStr">
         <is>
-          <t>Rafael Barros</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B75" s="33" t="inlineStr">
@@ -18394,13 +18402,13 @@
         </is>
       </c>
       <c r="C75" s="37" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D75" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="37" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F75" s="38" t="n">
         <v>190</v>
@@ -18411,7 +18419,7 @@
         </is>
       </c>
       <c r="H75" s="37" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="I75" s="24" t="str">
         <f>IF(A75="","",IF(G75="Sim","Paga",IF(E75="","Sem vencimento",IF(E75&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18445,7 +18453,7 @@
     <row r="76">
       <c r="A76" s="33" t="inlineStr">
         <is>
-          <t>Rafael Barros</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B76" s="33" t="inlineStr">
@@ -18454,13 +18462,13 @@
         </is>
       </c>
       <c r="C76" s="37" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="D76" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="37" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="F76" s="38" t="n">
         <v>190</v>
@@ -18471,7 +18479,7 @@
         </is>
       </c>
       <c r="H76" s="37" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="I76" s="24" t="str">
         <f>IF(A76="","",IF(G76="Sim","Paga",IF(E76="","Sem vencimento",IF(E76&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18505,7 +18513,7 @@
     <row r="77">
       <c r="A77" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Helena Moreira</t>
         </is>
       </c>
       <c r="B77" s="33" t="inlineStr">
@@ -18514,13 +18522,13 @@
         </is>
       </c>
       <c r="C77" s="37" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="D77" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E77" s="37" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F77" s="38" t="n">
         <v>380</v>
@@ -18531,7 +18539,7 @@
         </is>
       </c>
       <c r="H77" s="37" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="I77" s="24" t="str">
         <f>IF(A77="","",IF(G77="Sim","Paga",IF(E77="","Sem vencimento",IF(E77&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18565,7 +18573,7 @@
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="B78" s="33" t="inlineStr">
@@ -18625,7 +18633,7 @@
     <row r="79">
       <c r="A79" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="B79" s="33" t="inlineStr">
@@ -18685,25 +18693,25 @@
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>Rafael Dias</t>
+          <t>Fernanda Freitas</t>
         </is>
       </c>
       <c r="B80" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C80" s="37" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="D80" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E80" s="37" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F80" s="38" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="G80" s="35" t="inlineStr">
         <is>
@@ -18711,7 +18719,7 @@
         </is>
       </c>
       <c r="H80" s="37" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="I80" s="24" t="str">
         <f>IF(A80="","",IF(G80="Sim","Paga",IF(E80="","Sem vencimento",IF(E80&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18745,25 +18753,25 @@
     <row r="81">
       <c r="A81" s="33" t="inlineStr">
         <is>
-          <t>Fernanda Freitas</t>
+          <t>Rodrigo Moreira</t>
         </is>
       </c>
       <c r="B81" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C81" s="37" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="D81" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E81" s="37" t="n">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="F81" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G81" s="35" t="inlineStr">
         <is>
@@ -18771,7 +18779,7 @@
         </is>
       </c>
       <c r="H81" s="37" t="n">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="I81" s="24" t="str">
         <f>IF(A81="","",IF(G81="Sim","Paga",IF(E81="","Sem vencimento",IF(E81&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18805,25 +18813,25 @@
     <row r="82">
       <c r="A82" s="33" t="inlineStr">
         <is>
-          <t>Fernanda Freitas</t>
+          <t>Rodrigo Moreira</t>
         </is>
       </c>
       <c r="B82" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C82" s="37" t="n">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="D82" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E82" s="37" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F82" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G82" s="35" t="inlineStr">
         <is>
@@ -18831,7 +18839,7 @@
         </is>
       </c>
       <c r="H82" s="37" t="n">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="I82" s="24" t="str">
         <f>IF(A82="","",IF(G82="Sim","Paga",IF(E82="","Sem vencimento",IF(E82&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18865,25 +18873,25 @@
     <row r="83">
       <c r="A83" s="33" t="inlineStr">
         <is>
-          <t>Rodrigo Moreira</t>
+          <t>Roberta Araújo</t>
         </is>
       </c>
       <c r="B83" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Check-up cardiológico (consulta + ECG + teste ergométrico)</t>
         </is>
       </c>
       <c r="C83" s="37" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="D83" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E83" s="37" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="F83" s="38" t="n">
-        <v>380</v>
+        <v>960</v>
       </c>
       <c r="G83" s="35" t="inlineStr">
         <is>
@@ -18891,7 +18899,7 @@
         </is>
       </c>
       <c r="H83" s="37" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="I83" s="24" t="str">
         <f>IF(A83="","",IF(G83="Sim","Paga",IF(E83="","Sem vencimento",IF(E83&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18925,25 +18933,25 @@
     <row r="84">
       <c r="A84" s="33" t="inlineStr">
         <is>
-          <t>Roberta Araújo</t>
+          <t>Camila Freitas</t>
         </is>
       </c>
       <c r="B84" s="33" t="inlineStr">
         <is>
-          <t>Check-up cardiológico (consulta + ECG + teste ergométrico)</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C84" s="37" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D84" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E84" s="37" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="F84" s="38" t="n">
-        <v>960</v>
+        <v>190</v>
       </c>
       <c r="G84" s="35" t="inlineStr">
         <is>
@@ -18951,7 +18959,7 @@
         </is>
       </c>
       <c r="H84" s="37" t="n">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="I84" s="24" t="str">
         <f>IF(A84="","",IF(G84="Sim","Paga",IF(E84="","Sem vencimento",IF(E84&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -18985,25 +18993,25 @@
     <row r="85">
       <c r="A85" s="33" t="inlineStr">
         <is>
-          <t>Mônica Almeida</t>
+          <t>Camila Freitas</t>
         </is>
       </c>
       <c r="B85" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C85" s="37" t="n">
         <v>46154</v>
       </c>
       <c r="D85" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="37" t="n">
-        <v>46184</v>
+        <v>46214</v>
       </c>
       <c r="F85" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G85" s="35" t="inlineStr">
         <is>
@@ -19011,7 +19019,7 @@
         </is>
       </c>
       <c r="H85" s="37" t="n">
-        <v>46184</v>
+        <v>46216</v>
       </c>
       <c r="I85" s="24" t="str">
         <f>IF(A85="","",IF(G85="Sim","Paga",IF(E85="","Sem vencimento",IF(E85&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19045,7 +19053,7 @@
     <row r="86">
       <c r="A86" s="33" t="inlineStr">
         <is>
-          <t>Paulo Fernandes</t>
+          <t>Mônica Almeida</t>
         </is>
       </c>
       <c r="B86" s="33" t="inlineStr">
@@ -19063,7 +19071,7 @@
         <v>46184</v>
       </c>
       <c r="F86" s="38" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G86" s="35" t="inlineStr">
         <is>
@@ -19117,13 +19125,13 @@
         <v>46154</v>
       </c>
       <c r="D87" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="37" t="n">
-        <v>46214</v>
+        <v>46184</v>
       </c>
       <c r="F87" s="38" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G87" s="35" t="inlineStr">
         <is>
@@ -19131,7 +19139,7 @@
         </is>
       </c>
       <c r="H87" s="37" t="n">
-        <v>46216</v>
+        <v>46184</v>
       </c>
       <c r="I87" s="24" t="str">
         <f>IF(A87="","",IF(G87="Sim","Paga",IF(E87="","Sem vencimento",IF(E87&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19165,7 +19173,7 @@
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>Camila Freitas</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="B88" s="33" t="inlineStr">
@@ -19174,13 +19182,13 @@
         </is>
       </c>
       <c r="C88" s="37" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="D88" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="37" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="F88" s="38" t="n">
         <v>380</v>
@@ -19191,7 +19199,7 @@
         </is>
       </c>
       <c r="H88" s="37" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="I88" s="24" t="str">
         <f>IF(A88="","",IF(G88="Sim","Paga",IF(E88="","Sem vencimento",IF(E88&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19225,56 +19233,57 @@
     <row r="89">
       <c r="A89" s="33" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Beatriz Gomes</t>
         </is>
       </c>
       <c r="B89" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C89" s="37" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="D89" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="37">
-        <f>TODAY()-94</f>
-        <v>46185.0</v>
+      <c r="E89" s="37" t="n">
+        <v>46186</v>
       </c>
       <c r="F89" s="38" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="G89" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H89" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H89" s="37" t="n">
+        <v>46186</v>
+      </c>
       <c r="I89" s="24" t="str">
         <f>IF(A89="","",IF(G89="Sim","Paga",IF(E89="","Sem vencimento",IF(E89&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J89" s="30">
         <f>IF(I89="Vencida",Config!$B$5-E89,"")</f>
-        <v>94</v>
+        <v/>
       </c>
       <c r="K89" s="30">
         <f>IF(I89="A vencer",E89-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L89" s="24" t="str">
+      <c r="L89" s="24">
         <f>IF(I89&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J89)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J89))))</f>
-        <v>30 dias ou mais</v>
-      </c>
-      <c r="M89" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M89" s="23">
         <f>IF(I89&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J89)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J89))))</f>
-        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
+        <v/>
       </c>
       <c r="N89" s="39">
         <f>IF(I89="Vencida",F89*J89+ROW()/100000,0)</f>
-        <v>35720.00089</v>
+        <v>0</v>
       </c>
       <c r="O89" s="39">
         <f>IF(AND(I89="A vencer",K89&lt;=Config!$B$7),100000-K89-ROW()/100000,0)</f>
@@ -19284,25 +19293,25 @@
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Beatriz Gomes</t>
         </is>
       </c>
       <c r="B90" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C90" s="37" t="n">
         <v>46156</v>
       </c>
       <c r="D90" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="37" t="n">
-        <v>46186</v>
+        <v>46216</v>
       </c>
       <c r="F90" s="38" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="G90" s="35" t="inlineStr">
         <is>
@@ -19310,7 +19319,7 @@
         </is>
       </c>
       <c r="H90" s="37" t="n">
-        <v>46187</v>
+        <v>46216</v>
       </c>
       <c r="I90" s="24" t="str">
         <f>IF(A90="","",IF(G90="Sim","Paga",IF(E90="","Sem vencimento",IF(E90&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19344,7 +19353,7 @@
     <row r="91">
       <c r="A91" s="33" t="inlineStr">
         <is>
-          <t>Regina Macedo</t>
+          <t>Helena Moreira</t>
         </is>
       </c>
       <c r="B91" s="33" t="inlineStr">
@@ -19358,43 +19367,42 @@
       <c r="D91" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="37" t="n">
-        <v>46186</v>
+      <c r="E91" s="37">
+        <f>TODAY()-93</f>
+        <v>46186.0</v>
       </c>
       <c r="F91" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G91" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H91" s="37" t="n">
-        <v>46186</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H91" s="37" t="n"/>
       <c r="I91" s="24" t="str">
         <f>IF(A91="","",IF(G91="Sim","Paga",IF(E91="","Sem vencimento",IF(E91&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J91" s="30">
         <f>IF(I91="Vencida",Config!$B$5-E91,"")</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="K91" s="30">
         <f>IF(I91="A vencer",E91-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L91" s="24">
+      <c r="L91" s="24" t="str">
         <f>IF(I91&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J91)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J91))))</f>
-        <v/>
-      </c>
-      <c r="M91" s="23">
+        <v>30 dias ou mais</v>
+      </c>
+      <c r="M91" s="23" t="str">
         <f>IF(I91&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J91)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J91))))</f>
-        <v/>
+        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
       </c>
       <c r="N91" s="39">
         <f>IF(I91="Vencida",F91*J91+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>35340.00091</v>
       </c>
       <c r="O91" s="39">
         <f>IF(AND(I91="A vencer",K91&lt;=Config!$B$7),100000-K91-ROW()/100000,0)</f>
@@ -19416,13 +19424,13 @@
         <v>46156</v>
       </c>
       <c r="D92" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="37" t="n">
-        <v>46216</v>
+        <v>46186</v>
       </c>
       <c r="F92" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G92" s="35" t="inlineStr">
         <is>
@@ -19430,7 +19438,7 @@
         </is>
       </c>
       <c r="H92" s="37" t="n">
-        <v>46216</v>
+        <v>46187</v>
       </c>
       <c r="I92" s="24" t="str">
         <f>IF(A92="","",IF(G92="Sim","Paga",IF(E92="","Sem vencimento",IF(E92&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19464,25 +19472,25 @@
     <row r="93">
       <c r="A93" s="33" t="inlineStr">
         <is>
-          <t>Beatriz Gomes</t>
+          <t>Leandro Oliveira</t>
         </is>
       </c>
       <c r="B93" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C93" s="37" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D93" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E93" s="37" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="F93" s="38" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G93" s="35" t="inlineStr">
         <is>
@@ -19490,7 +19498,7 @@
         </is>
       </c>
       <c r="H93" s="37" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="I93" s="24" t="str">
         <f>IF(A93="","",IF(G93="Sim","Paga",IF(E93="","Sem vencimento",IF(E93&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19524,25 +19532,25 @@
     <row r="94">
       <c r="A94" s="33" t="inlineStr">
         <is>
-          <t>Beatriz Gomes</t>
+          <t>Leandro Oliveira</t>
         </is>
       </c>
       <c r="B94" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C94" s="37" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="D94" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E94" s="37" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="F94" s="38" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G94" s="35" t="inlineStr">
         <is>
@@ -19550,7 +19558,7 @@
         </is>
       </c>
       <c r="H94" s="37" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="I94" s="24" t="str">
         <f>IF(A94="","",IF(G94="Sim","Paga",IF(E94="","Sem vencimento",IF(E94&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19584,25 +19592,25 @@
     <row r="95">
       <c r="A95" s="33" t="inlineStr">
         <is>
-          <t>Leandro Oliveira</t>
+          <t>Fábio Correia</t>
         </is>
       </c>
       <c r="B95" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C95" s="37" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D95" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="37" t="n">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="F95" s="38" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="G95" s="35" t="inlineStr">
         <is>
@@ -19610,7 +19618,7 @@
         </is>
       </c>
       <c r="H95" s="37" t="n">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="I95" s="24" t="str">
         <f>IF(A95="","",IF(G95="Sim","Paga",IF(E95="","Sem vencimento",IF(E95&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19644,12 +19652,12 @@
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>Fábio Correia</t>
+          <t>Wagner Lima</t>
         </is>
       </c>
       <c r="B96" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Check-up cardiológico (consulta + ECG + teste ergométrico)</t>
         </is>
       </c>
       <c r="C96" s="37" t="n">
@@ -19662,7 +19670,7 @@
         <v>46190</v>
       </c>
       <c r="F96" s="38" t="n">
-        <v>190</v>
+        <v>480</v>
       </c>
       <c r="G96" s="35" t="inlineStr">
         <is>
@@ -19704,12 +19712,12 @@
     <row r="97">
       <c r="A97" s="33" t="inlineStr">
         <is>
-          <t>Fábio Correia</t>
+          <t>Wagner Lima</t>
         </is>
       </c>
       <c r="B97" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Check-up cardiológico (consulta + ECG + teste ergométrico)</t>
         </is>
       </c>
       <c r="C97" s="37" t="n">
@@ -19722,7 +19730,7 @@
         <v>46220</v>
       </c>
       <c r="F97" s="38" t="n">
-        <v>190</v>
+        <v>480</v>
       </c>
       <c r="G97" s="35" t="inlineStr">
         <is>
@@ -19764,25 +19772,25 @@
     <row r="98">
       <c r="A98" s="33" t="inlineStr">
         <is>
-          <t>Wagner Lima</t>
+          <t>Otávio Nascimento</t>
         </is>
       </c>
       <c r="B98" s="33" t="inlineStr">
         <is>
-          <t>Check-up cardiológico (consulta + ECG + teste ergométrico)</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C98" s="37" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="D98" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E98" s="37" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="F98" s="38" t="n">
-        <v>960</v>
+        <v>300</v>
       </c>
       <c r="G98" s="35" t="inlineStr">
         <is>
@@ -19790,7 +19798,7 @@
         </is>
       </c>
       <c r="H98" s="37" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="I98" s="24" t="str">
         <f>IF(A98="","",IF(G98="Sim","Paga",IF(E98="","Sem vencimento",IF(E98&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19824,26 +19832,26 @@
     <row r="99">
       <c r="A99" s="33" t="inlineStr">
         <is>
-          <t>Otávio Nascimento</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B99" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C99" s="37" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="D99" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E99" s="37">
-        <f>TODAY()-88</f>
-        <v>46191.0</v>
+        <f>TODAY()-87</f>
+        <v>46192.0</v>
       </c>
       <c r="F99" s="38" t="n">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="G99" s="35" t="inlineStr">
         <is>
@@ -19857,7 +19865,7 @@
       </c>
       <c r="J99" s="30">
         <f>IF(I99="Vencida",Config!$B$5-E99,"")</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K99" s="30">
         <f>IF(I99="A vencer",E99-Config!$B$5,"")</f>
@@ -19873,7 +19881,7 @@
       </c>
       <c r="N99" s="39">
         <f>IF(I99="Vencida",F99*J99+ROW()/100000,0)</f>
-        <v>26400.00099</v>
+        <v>33060.00099</v>
       </c>
       <c r="O99" s="39">
         <f>IF(AND(I99="A vencer",K99&lt;=Config!$B$7),100000-K99-ROW()/100000,0)</f>
@@ -19883,7 +19891,7 @@
     <row r="100">
       <c r="A100" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Paulo Reis</t>
         </is>
       </c>
       <c r="B100" s="33" t="inlineStr">
@@ -19892,13 +19900,13 @@
         </is>
       </c>
       <c r="C100" s="37" t="n">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="D100" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E100" s="37" t="n">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="F100" s="38" t="n">
         <v>380</v>
@@ -19909,7 +19917,7 @@
         </is>
       </c>
       <c r="H100" s="37" t="n">
-        <v>46193</v>
+        <v>46198</v>
       </c>
       <c r="I100" s="24" t="str">
         <f>IF(A100="","",IF(G100="Sim","Paga",IF(E100="","Sem vencimento",IF(E100&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -19943,7 +19951,7 @@
     <row r="101">
       <c r="A101" s="33" t="inlineStr">
         <is>
-          <t>Márcia Duarte</t>
+          <t>Camila Dias</t>
         </is>
       </c>
       <c r="B101" s="33" t="inlineStr">
@@ -19952,13 +19960,13 @@
         </is>
       </c>
       <c r="C101" s="37" t="n">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="D101" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E101" s="37" t="n">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="F101" s="38" t="n">
         <v>400</v>
@@ -19969,7 +19977,7 @@
         </is>
       </c>
       <c r="H101" s="37" t="n">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="I101" s="24" t="str">
         <f>IF(A101="","",IF(G101="Sim","Paga",IF(E101="","Sem vencimento",IF(E101&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20003,7 +20011,7 @@
     <row r="102">
       <c r="A102" s="33" t="inlineStr">
         <is>
-          <t>Paulo Reis</t>
+          <t>Elaine Cardoso</t>
         </is>
       </c>
       <c r="B102" s="33" t="inlineStr">
@@ -20012,47 +20020,48 @@
         </is>
       </c>
       <c r="C102" s="37" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="D102" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="37">
-        <f>TODAY()-82</f>
-        <v>46197.0</v>
+      <c r="E102" s="37" t="n">
+        <v>46200</v>
       </c>
       <c r="F102" s="38" t="n">
         <v>380</v>
       </c>
       <c r="G102" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H102" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H102" s="37" t="n">
+        <v>46201</v>
+      </c>
       <c r="I102" s="24" t="str">
         <f>IF(A102="","",IF(G102="Sim","Paga",IF(E102="","Sem vencimento",IF(E102&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J102" s="30">
         <f>IF(I102="Vencida",Config!$B$5-E102,"")</f>
-        <v>82</v>
+        <v/>
       </c>
       <c r="K102" s="30">
         <f>IF(I102="A vencer",E102-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L102" s="24" t="str">
+      <c r="L102" s="24">
         <f>IF(I102&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J102)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J102))))</f>
-        <v>30 dias ou mais</v>
-      </c>
-      <c r="M102" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M102" s="23">
         <f>IF(I102&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J102)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J102))))</f>
-        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
+        <v/>
       </c>
       <c r="N102" s="39">
         <f>IF(I102="Vencida",F102*J102+ROW()/100000,0)</f>
-        <v>31160.00102</v>
+        <v>0</v>
       </c>
       <c r="O102" s="39">
         <f>IF(AND(I102="A vencer",K102&lt;=Config!$B$7),100000-K102-ROW()/100000,0)</f>
@@ -20062,7 +20071,7 @@
     <row r="103">
       <c r="A103" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Mariana Nascimento</t>
         </is>
       </c>
       <c r="B103" s="33" t="inlineStr">
@@ -20076,43 +20085,42 @@
       <c r="D103" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="37" t="n">
-        <v>46200</v>
+      <c r="E103" s="37">
+        <f>TODAY()-79</f>
+        <v>46200.0</v>
       </c>
       <c r="F103" s="38" t="n">
         <v>380</v>
       </c>
       <c r="G103" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H103" s="37" t="n">
-        <v>46200</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H103" s="37" t="n"/>
       <c r="I103" s="24" t="str">
         <f>IF(A103="","",IF(G103="Sim","Paga",IF(E103="","Sem vencimento",IF(E103&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J103" s="30">
         <f>IF(I103="Vencida",Config!$B$5-E103,"")</f>
-        <v/>
+        <v>79</v>
       </c>
       <c r="K103" s="30">
         <f>IF(I103="A vencer",E103-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L103" s="24">
+      <c r="L103" s="24" t="str">
         <f>IF(I103&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J103)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J103))))</f>
-        <v/>
-      </c>
-      <c r="M103" s="23">
+        <v>30 dias ou mais</v>
+      </c>
+      <c r="M103" s="23" t="str">
         <f>IF(I103&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J103)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J103))))</f>
-        <v/>
+        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
       </c>
       <c r="N103" s="39">
         <f>IF(I103="Vencida",F103*J103+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>30020.00103</v>
       </c>
       <c r="O103" s="39">
         <f>IF(AND(I103="A vencer",K103&lt;=Config!$B$7),100000-K103-ROW()/100000,0)</f>
@@ -20122,7 +20130,7 @@
     <row r="104">
       <c r="A104" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Gustavo Pinto</t>
         </is>
       </c>
       <c r="B104" s="33" t="inlineStr">
@@ -20131,13 +20139,13 @@
         </is>
       </c>
       <c r="C104" s="37" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D104" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E104" s="37" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="F104" s="38" t="n">
         <v>190</v>
@@ -20148,7 +20156,7 @@
         </is>
       </c>
       <c r="H104" s="37" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="I104" s="24" t="str">
         <f>IF(A104="","",IF(G104="Sim","Paga",IF(E104="","Sem vencimento",IF(E104&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20182,7 +20190,7 @@
     <row r="105">
       <c r="A105" s="33" t="inlineStr">
         <is>
-          <t>Mariana Nascimento</t>
+          <t>Gustavo Pinto</t>
         </is>
       </c>
       <c r="B105" s="33" t="inlineStr">
@@ -20191,13 +20199,13 @@
         </is>
       </c>
       <c r="C105" s="37" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D105" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E105" s="37" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F105" s="38" t="n">
         <v>190</v>
@@ -20208,7 +20216,7 @@
         </is>
       </c>
       <c r="H105" s="37" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="I105" s="24" t="str">
         <f>IF(A105="","",IF(G105="Sim","Paga",IF(E105="","Sem vencimento",IF(E105&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20242,25 +20250,25 @@
     <row r="106">
       <c r="A106" s="33" t="inlineStr">
         <is>
-          <t>Camila Dias</t>
+          <t>Marcelo Moreira</t>
         </is>
       </c>
       <c r="B106" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C106" s="37" t="n">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="D106" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E106" s="37" t="n">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="F106" s="38" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G106" s="35" t="inlineStr">
         <is>
@@ -20268,7 +20276,7 @@
         </is>
       </c>
       <c r="H106" s="37" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="I106" s="24" t="str">
         <f>IF(A106="","",IF(G106="Sim","Paga",IF(E106="","Sem vencimento",IF(E106&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20302,25 +20310,25 @@
     <row r="107">
       <c r="A107" s="33" t="inlineStr">
         <is>
-          <t>Gustavo Pinto</t>
+          <t>Marcelo Moreira</t>
         </is>
       </c>
       <c r="B107" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="C107" s="37" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="D107" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="37" t="n">
-        <v>46201</v>
+        <v>46235</v>
       </c>
       <c r="F107" s="38" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="G107" s="35" t="inlineStr">
         <is>
@@ -20328,7 +20336,7 @@
         </is>
       </c>
       <c r="H107" s="37" t="n">
-        <v>46203</v>
+        <v>46240</v>
       </c>
       <c r="I107" s="24" t="str">
         <f>IF(A107="","",IF(G107="Sim","Paga",IF(E107="","Sem vencimento",IF(E107&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20362,7 +20370,7 @@
     <row r="108">
       <c r="A108" s="33" t="inlineStr">
         <is>
-          <t>Gustavo Pinto</t>
+          <t>Wagner Costa</t>
         </is>
       </c>
       <c r="B108" s="33" t="inlineStr">
@@ -20371,16 +20379,16 @@
         </is>
       </c>
       <c r="C108" s="37" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="D108" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="37" t="n">
-        <v>46231</v>
+        <v>46205</v>
       </c>
       <c r="F108" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G108" s="35" t="inlineStr">
         <is>
@@ -20388,7 +20396,7 @@
         </is>
       </c>
       <c r="H108" s="37" t="n">
-        <v>46236</v>
+        <v>46205</v>
       </c>
       <c r="I108" s="24" t="str">
         <f>IF(A108="","",IF(G108="Sim","Paga",IF(E108="","Sem vencimento",IF(E108&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20422,7 +20430,7 @@
     <row r="109">
       <c r="A109" s="33" t="inlineStr">
         <is>
-          <t>Wagner Costa</t>
+          <t>Ana Costa</t>
         </is>
       </c>
       <c r="B109" s="33" t="inlineStr">
@@ -20431,13 +20439,13 @@
         </is>
       </c>
       <c r="C109" s="37" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="D109" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E109" s="37" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F109" s="38" t="n">
         <v>380</v>
@@ -20448,7 +20456,7 @@
         </is>
       </c>
       <c r="H109" s="37" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="I109" s="24" t="str">
         <f>IF(A109="","",IF(G109="Sim","Paga",IF(E109="","Sem vencimento",IF(E109&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20482,25 +20490,25 @@
     <row r="110">
       <c r="A110" s="33" t="inlineStr">
         <is>
-          <t>Marcelo Moreira</t>
+          <t>Regina Teixeira</t>
         </is>
       </c>
       <c r="B110" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C110" s="37" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="D110" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E110" s="37" t="n">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F110" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G110" s="35" t="inlineStr">
         <is>
@@ -20508,7 +20516,7 @@
         </is>
       </c>
       <c r="H110" s="37" t="n">
-        <v>46208</v>
+        <v>46216</v>
       </c>
       <c r="I110" s="24" t="str">
         <f>IF(A110="","",IF(G110="Sim","Paga",IF(E110="","Sem vencimento",IF(E110&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20542,25 +20550,25 @@
     <row r="111">
       <c r="A111" s="33" t="inlineStr">
         <is>
-          <t>Marcelo Moreira</t>
+          <t>Regina Teixeira</t>
         </is>
       </c>
       <c r="B111" s="33" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C111" s="37" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="D111" s="35" t="n">
         <v>2</v>
       </c>
       <c r="E111" s="37" t="n">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="F111" s="38" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="G111" s="35" t="inlineStr">
         <is>
@@ -20568,7 +20576,7 @@
         </is>
       </c>
       <c r="H111" s="37" t="n">
-        <v>46235</v>
+        <v>46243</v>
       </c>
       <c r="I111" s="24" t="str">
         <f>IF(A111="","",IF(G111="Sim","Paga",IF(E111="","Sem vencimento",IF(E111&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20602,25 +20610,25 @@
     <row r="112">
       <c r="A112" s="33" t="inlineStr">
         <is>
-          <t>Ana Costa</t>
+          <t>Leandro Oliveira</t>
         </is>
       </c>
       <c r="B112" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>ECG</t>
         </is>
       </c>
       <c r="C112" s="37" t="n">
-        <v>46176</v>
+        <v>46185</v>
       </c>
       <c r="D112" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E112" s="37" t="n">
-        <v>46206</v>
+        <v>46215</v>
       </c>
       <c r="F112" s="38" t="n">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="G112" s="35" t="inlineStr">
         <is>
@@ -20628,7 +20636,7 @@
         </is>
       </c>
       <c r="H112" s="37" t="n">
-        <v>46206</v>
+        <v>46215</v>
       </c>
       <c r="I112" s="24" t="str">
         <f>IF(A112="","",IF(G112="Sim","Paga",IF(E112="","Sem vencimento",IF(E112&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20662,7 +20670,7 @@
     <row r="113">
       <c r="A113" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Cláudia Costa</t>
         </is>
       </c>
       <c r="B113" s="33" t="inlineStr">
@@ -20671,16 +20679,16 @@
         </is>
       </c>
       <c r="C113" s="37" t="n">
-        <v>46176</v>
+        <v>46188</v>
       </c>
       <c r="D113" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E113" s="37" t="n">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="F113" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G113" s="35" t="inlineStr">
         <is>
@@ -20688,7 +20696,7 @@
         </is>
       </c>
       <c r="H113" s="37" t="n">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="I113" s="24" t="str">
         <f>IF(A113="","",IF(G113="Sim","Paga",IF(E113="","Sem vencimento",IF(E113&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20722,7 +20730,7 @@
     <row r="114">
       <c r="A114" s="33" t="inlineStr">
         <is>
-          <t>Regina Teixeira</t>
+          <t>Cláudia Costa</t>
         </is>
       </c>
       <c r="B114" s="33" t="inlineStr">
@@ -20731,16 +20739,16 @@
         </is>
       </c>
       <c r="C114" s="37" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="D114" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" s="37" t="n">
-        <v>46213</v>
+        <v>46248</v>
       </c>
       <c r="F114" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G114" s="35" t="inlineStr">
         <is>
@@ -20748,7 +20756,7 @@
         </is>
       </c>
       <c r="H114" s="37" t="n">
-        <v>46215</v>
+        <v>46251</v>
       </c>
       <c r="I114" s="24" t="str">
         <f>IF(A114="","",IF(G114="Sim","Paga",IF(E114="","Sem vencimento",IF(E114&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20782,25 +20790,25 @@
     <row r="115">
       <c r="A115" s="33" t="inlineStr">
         <is>
-          <t>Leandro Oliveira</t>
+          <t>Rafael Barros</t>
         </is>
       </c>
       <c r="B115" s="33" t="inlineStr">
         <is>
-          <t>ECG</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="C115" s="37" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="D115" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E115" s="37" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="F115" s="38" t="n">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="G115" s="35" t="inlineStr">
         <is>
@@ -20808,7 +20816,7 @@
         </is>
       </c>
       <c r="H115" s="37" t="n">
-        <v>46215</v>
+        <v>46223</v>
       </c>
       <c r="I115" s="24" t="str">
         <f>IF(A115="","",IF(G115="Sim","Paga",IF(E115="","Sem vencimento",IF(E115&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20842,57 +20850,56 @@
     <row r="116">
       <c r="A116" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Costa</t>
+          <t>Rafael Barros</t>
         </is>
       </c>
       <c r="B116" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="C116" s="37" t="n">
         <v>46188</v>
       </c>
       <c r="D116" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="37" t="n">
-        <v>46218</v>
+        <v>2</v>
+      </c>
+      <c r="E116" s="37">
+        <f>TODAY()-31</f>
+        <v>46248.0</v>
       </c>
       <c r="F116" s="38" t="n">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G116" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H116" s="37" t="n">
-        <v>46219</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H116" s="37" t="n"/>
       <c r="I116" s="24" t="str">
         <f>IF(A116="","",IF(G116="Sim","Paga",IF(E116="","Sem vencimento",IF(E116&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J116" s="30">
         <f>IF(I116="Vencida",Config!$B$5-E116,"")</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="K116" s="30">
         <f>IF(I116="A vencer",E116-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L116" s="24">
+      <c r="L116" s="24" t="str">
         <f>IF(I116&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J116)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J116))))</f>
-        <v/>
-      </c>
-      <c r="M116" s="23">
+        <v>30 dias ou mais</v>
+      </c>
+      <c r="M116" s="23" t="str">
         <f>IF(I116&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J116)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J116))))</f>
-        <v/>
+        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
       </c>
       <c r="N116" s="39">
         <f>IF(I116="Vencida",F116*J116+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>5425.00116</v>
       </c>
       <c r="O116" s="39">
         <f>IF(AND(I116="A vencer",K116&lt;=Config!$B$7),100000-K116-ROW()/100000,0)</f>
@@ -20902,7 +20909,7 @@
     <row r="117">
       <c r="A117" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Costa</t>
+          <t>Gabriel Oliveira</t>
         </is>
       </c>
       <c r="B117" s="33" t="inlineStr">
@@ -20911,16 +20918,16 @@
         </is>
       </c>
       <c r="C117" s="37" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D117" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="37" t="n">
-        <v>46248</v>
+        <v>46219</v>
       </c>
       <c r="F117" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G117" s="35" t="inlineStr">
         <is>
@@ -20928,7 +20935,7 @@
         </is>
       </c>
       <c r="H117" s="37" t="n">
-        <v>46253</v>
+        <v>46219</v>
       </c>
       <c r="I117" s="24" t="str">
         <f>IF(A117="","",IF(G117="Sim","Paga",IF(E117="","Sem vencimento",IF(E117&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -20962,25 +20969,25 @@
     <row r="118">
       <c r="A118" s="33" t="inlineStr">
         <is>
-          <t>Rafael Barros</t>
+          <t>Mariana Gomes</t>
         </is>
       </c>
       <c r="B118" s="33" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C118" s="37" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="D118" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E118" s="37" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="F118" s="38" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G118" s="35" t="inlineStr">
         <is>
@@ -20988,7 +20995,7 @@
         </is>
       </c>
       <c r="H118" s="37" t="n">
-        <v>46218</v>
+        <v>46221</v>
       </c>
       <c r="I118" s="24" t="str">
         <f>IF(A118="","",IF(G118="Sim","Paga",IF(E118="","Sem vencimento",IF(E118&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21040,7 +21047,7 @@
         <v>46219</v>
       </c>
       <c r="F119" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G119" s="35" t="inlineStr">
         <is>
@@ -21048,7 +21055,7 @@
         </is>
       </c>
       <c r="H119" s="37" t="n">
-        <v>46221</v>
+        <v>46220</v>
       </c>
       <c r="I119" s="24" t="str">
         <f>IF(A119="","",IF(G119="Sim","Paga",IF(E119="","Sem vencimento",IF(E119&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21082,7 +21089,7 @@
     <row r="120">
       <c r="A120" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Oliveira</t>
+          <t>Otávio Cardoso</t>
         </is>
       </c>
       <c r="B120" s="33" t="inlineStr">
@@ -21094,10 +21101,10 @@
         <v>46189</v>
       </c>
       <c r="D120" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="37" t="n">
-        <v>46219</v>
+        <v>46249</v>
       </c>
       <c r="F120" s="38" t="n">
         <v>190</v>
@@ -21108,7 +21115,7 @@
         </is>
       </c>
       <c r="H120" s="37" t="n">
-        <v>46219</v>
+        <v>46254</v>
       </c>
       <c r="I120" s="24" t="str">
         <f>IF(A120="","",IF(G120="Sim","Paga",IF(E120="","Sem vencimento",IF(E120&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21142,7 +21149,7 @@
     <row r="121">
       <c r="A121" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Oliveira</t>
+          <t>Viviane Ribeiro</t>
         </is>
       </c>
       <c r="B121" s="33" t="inlineStr">
@@ -21151,13 +21158,13 @@
         </is>
       </c>
       <c r="C121" s="37" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D121" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="37" t="n">
-        <v>46249</v>
+        <v>46220</v>
       </c>
       <c r="F121" s="38" t="n">
         <v>190</v>
@@ -21168,7 +21175,7 @@
         </is>
       </c>
       <c r="H121" s="37" t="n">
-        <v>46249</v>
+        <v>46220</v>
       </c>
       <c r="I121" s="24" t="str">
         <f>IF(A121="","",IF(G121="Sim","Paga",IF(E121="","Sem vencimento",IF(E121&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21202,25 +21209,25 @@
     <row r="122">
       <c r="A122" s="33" t="inlineStr">
         <is>
-          <t>Gabriel Reis</t>
+          <t>Viviane Ribeiro</t>
         </is>
       </c>
       <c r="B122" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C122" s="37" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="D122" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="37" t="n">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="F122" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G122" s="35" t="inlineStr">
         <is>
@@ -21228,7 +21235,7 @@
         </is>
       </c>
       <c r="H122" s="37" t="n">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="I122" s="24" t="str">
         <f>IF(A122="","",IF(G122="Sim","Paga",IF(E122="","Sem vencimento",IF(E122&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21262,25 +21269,25 @@
     <row r="123">
       <c r="A123" s="33" t="inlineStr">
         <is>
-          <t>Mariana Gomes</t>
+          <t>Gustavo Ferreira</t>
         </is>
       </c>
       <c r="B123" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C123" s="37" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="D123" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E123" s="37" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="F123" s="38" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G123" s="35" t="inlineStr">
         <is>
@@ -21322,7 +21329,7 @@
     <row r="124">
       <c r="A124" s="33" t="inlineStr">
         <is>
-          <t>Viviane Ribeiro</t>
+          <t>Cláudia Costa</t>
         </is>
       </c>
       <c r="B124" s="33" t="inlineStr">
@@ -21331,14 +21338,14 @@
         </is>
       </c>
       <c r="C124" s="37" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="D124" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E124" s="37">
-        <f>TODAY()-59</f>
-        <v>46220.0</v>
+        <f>TODAY()-54</f>
+        <v>46225.0</v>
       </c>
       <c r="F124" s="38" t="n">
         <v>380</v>
@@ -21355,7 +21362,7 @@
       </c>
       <c r="J124" s="30">
         <f>IF(I124="Vencida",Config!$B$5-E124,"")</f>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K124" s="30">
         <f>IF(I124="A vencer",E124-Config!$B$5,"")</f>
@@ -21371,7 +21378,7 @@
       </c>
       <c r="N124" s="39">
         <f>IF(I124="Vencida",F124*J124+ROW()/100000,0)</f>
-        <v>22420.00124</v>
+        <v>20520.00124</v>
       </c>
       <c r="O124" s="39">
         <f>IF(AND(I124="A vencer",K124&lt;=Config!$B$7),100000-K124-ROW()/100000,0)</f>
@@ -21381,7 +21388,7 @@
     <row r="125">
       <c r="A125" s="33" t="inlineStr">
         <is>
-          <t>Gustavo Ferreira</t>
+          <t>Elaine Cardoso</t>
         </is>
       </c>
       <c r="B125" s="33" t="inlineStr">
@@ -21390,13 +21397,13 @@
         </is>
       </c>
       <c r="C125" s="37" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="D125" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="37" t="n">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="F125" s="38" t="n">
         <v>380</v>
@@ -21407,7 +21414,7 @@
         </is>
       </c>
       <c r="H125" s="37" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="I125" s="24" t="str">
         <f>IF(A125="","",IF(G125="Sim","Paga",IF(E125="","Sem vencimento",IF(E125&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21441,7 +21448,7 @@
     <row r="126">
       <c r="A126" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Fábio Machado</t>
         </is>
       </c>
       <c r="B126" s="33" t="inlineStr">
@@ -21450,16 +21457,16 @@
         </is>
       </c>
       <c r="C126" s="37" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D126" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E126" s="37" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F126" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G126" s="35" t="inlineStr">
         <is>
@@ -21467,7 +21474,7 @@
         </is>
       </c>
       <c r="H126" s="37" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="I126" s="24" t="str">
         <f>IF(A126="","",IF(G126="Sim","Paga",IF(E126="","Sem vencimento",IF(E126&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21501,25 +21508,25 @@
     <row r="127">
       <c r="A127" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="B127" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C127" s="37" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D127" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="37" t="n">
-        <v>46255</v>
+        <v>46226</v>
       </c>
       <c r="F127" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G127" s="35" t="inlineStr">
         <is>
@@ -21527,7 +21534,7 @@
         </is>
       </c>
       <c r="H127" s="37" t="n">
-        <v>46260</v>
+        <v>46227</v>
       </c>
       <c r="I127" s="24" t="str">
         <f>IF(A127="","",IF(G127="Sim","Paga",IF(E127="","Sem vencimento",IF(E127&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21561,25 +21568,25 @@
     <row r="128">
       <c r="A128" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Costa</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="B128" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C128" s="37" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D128" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" s="37" t="n">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="F128" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G128" s="35" t="inlineStr">
         <is>
@@ -21587,7 +21594,7 @@
         </is>
       </c>
       <c r="H128" s="37" t="n">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="I128" s="24" t="str">
         <f>IF(A128="","",IF(G128="Sim","Paga",IF(E128="","Sem vencimento",IF(E128&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21621,25 +21628,25 @@
     <row r="129">
       <c r="A129" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Costa</t>
+          <t>Patrícia Dias</t>
         </is>
       </c>
       <c r="B129" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C129" s="37" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="D129" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="37" t="n">
-        <v>46255</v>
+        <v>46233</v>
       </c>
       <c r="F129" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G129" s="35" t="inlineStr">
         <is>
@@ -21647,7 +21654,7 @@
         </is>
       </c>
       <c r="H129" s="37" t="n">
-        <v>46258</v>
+        <v>46238</v>
       </c>
       <c r="I129" s="24" t="str">
         <f>IF(A129="","",IF(G129="Sim","Paga",IF(E129="","Sem vencimento",IF(E129&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21681,25 +21688,25 @@
     <row r="130">
       <c r="A130" s="33" t="inlineStr">
         <is>
-          <t>Fábio Machado</t>
+          <t>Patrícia Dias</t>
         </is>
       </c>
       <c r="B130" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C130" s="37" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="D130" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="37" t="n">
-        <v>46226</v>
+        <v>46263</v>
       </c>
       <c r="F130" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G130" s="35" t="inlineStr">
         <is>
@@ -21707,7 +21714,7 @@
         </is>
       </c>
       <c r="H130" s="37" t="n">
-        <v>46227</v>
+        <v>46266</v>
       </c>
       <c r="I130" s="24" t="str">
         <f>IF(A130="","",IF(G130="Sim","Paga",IF(E130="","Sem vencimento",IF(E130&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21741,25 +21748,25 @@
     <row r="131">
       <c r="A131" s="33" t="inlineStr">
         <is>
-          <t>Fábio Machado</t>
+          <t>Roberta Lima</t>
         </is>
       </c>
       <c r="B131" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C131" s="37" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="D131" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="37" t="n">
-        <v>46256</v>
+        <v>46233</v>
       </c>
       <c r="F131" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G131" s="35" t="inlineStr">
         <is>
@@ -21767,7 +21774,7 @@
         </is>
       </c>
       <c r="H131" s="37" t="n">
-        <v>46256</v>
+        <v>46234</v>
       </c>
       <c r="I131" s="24" t="str">
         <f>IF(A131="","",IF(G131="Sim","Paga",IF(E131="","Sem vencimento",IF(E131&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21801,7 +21808,7 @@
     <row r="132">
       <c r="A132" s="33" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Roberta Lima</t>
         </is>
       </c>
       <c r="B132" s="33" t="inlineStr">
@@ -21810,47 +21817,48 @@
         </is>
       </c>
       <c r="C132" s="37" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="D132" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="37">
-        <f>TODAY()-53</f>
-        <v>46226.0</v>
+        <v>2</v>
+      </c>
+      <c r="E132" s="37" t="n">
+        <v>46263</v>
       </c>
       <c r="F132" s="38" t="n">
         <v>200</v>
       </c>
       <c r="G132" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H132" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H132" s="37" t="n">
+        <v>46263</v>
+      </c>
       <c r="I132" s="24" t="str">
         <f>IF(A132="","",IF(G132="Sim","Paga",IF(E132="","Sem vencimento",IF(E132&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J132" s="30">
         <f>IF(I132="Vencida",Config!$B$5-E132,"")</f>
-        <v>53</v>
+        <v/>
       </c>
       <c r="K132" s="30">
         <f>IF(I132="A vencer",E132-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L132" s="24" t="str">
+      <c r="L132" s="24">
         <f>IF(I132&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J132)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J132))))</f>
-        <v>30 dias ou mais</v>
-      </c>
-      <c r="M132" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M132" s="23">
         <f>IF(I132&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J132)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J132))))</f>
-        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
+        <v/>
       </c>
       <c r="N132" s="39">
         <f>IF(I132="Vencida",F132*J132+ROW()/100000,0)</f>
-        <v>10600.00132</v>
+        <v>0</v>
       </c>
       <c r="O132" s="39">
         <f>IF(AND(I132="A vencer",K132&lt;=Config!$B$7),100000-K132-ROW()/100000,0)</f>
@@ -21860,57 +21868,56 @@
     <row r="133">
       <c r="A133" s="33" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Carlos Fernandes</t>
         </is>
       </c>
       <c r="B133" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C133" s="37" t="n">
-        <v>46196</v>
+        <v>46209</v>
       </c>
       <c r="D133" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E133" s="37" t="n">
-        <v>46256</v>
+        <v>1</v>
+      </c>
+      <c r="E133" s="37">
+        <f>TODAY()-40</f>
+        <v>46239.0</v>
       </c>
       <c r="F133" s="38" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G133" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H133" s="37" t="n">
-        <v>46256</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H133" s="37" t="n"/>
       <c r="I133" s="24" t="str">
         <f>IF(A133="","",IF(G133="Sim","Paga",IF(E133="","Sem vencimento",IF(E133&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J133" s="30">
         <f>IF(I133="Vencida",Config!$B$5-E133,"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="K133" s="30">
         <f>IF(I133="A vencer",E133-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L133" s="24">
+      <c r="L133" s="24" t="str">
         <f>IF(I133&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J133)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J133))))</f>
-        <v/>
-      </c>
-      <c r="M133" s="23">
+        <v>30 dias ou mais</v>
+      </c>
+      <c r="M133" s="23" t="str">
         <f>IF(I133&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J133)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J133))))</f>
-        <v/>
+        <v>Conversa do médico ou da administração para combinar um plano de pagamento; registrar por escrito o que foi combinado.</v>
       </c>
       <c r="N133" s="39">
         <f>IF(I133="Vencida",F133*J133+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>7600.00133</v>
       </c>
       <c r="O133" s="39">
         <f>IF(AND(I133="A vencer",K133&lt;=Config!$B$7),100000-K133-ROW()/100000,0)</f>
@@ -21920,7 +21927,7 @@
     <row r="134">
       <c r="A134" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Carlos Fernandes</t>
         </is>
       </c>
       <c r="B134" s="33" t="inlineStr">
@@ -21929,16 +21936,16 @@
         </is>
       </c>
       <c r="C134" s="37" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="D134" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="37" t="n">
-        <v>46228</v>
+        <v>46269</v>
       </c>
       <c r="F134" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G134" s="35" t="inlineStr">
         <is>
@@ -21946,7 +21953,7 @@
         </is>
       </c>
       <c r="H134" s="37" t="n">
-        <v>46230</v>
+        <v>46269</v>
       </c>
       <c r="I134" s="24" t="str">
         <f>IF(A134="","",IF(G134="Sim","Paga",IF(E134="","Sem vencimento",IF(E134&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -21980,25 +21987,25 @@
     <row r="135">
       <c r="A135" s="33" t="inlineStr">
         <is>
-          <t>Patrícia Dias</t>
+          <t>Gustavo Ferreira</t>
         </is>
       </c>
       <c r="B135" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C135" s="37" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="D135" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E135" s="37" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="F135" s="38" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G135" s="35" t="inlineStr">
         <is>
@@ -22006,7 +22013,7 @@
         </is>
       </c>
       <c r="H135" s="37" t="n">
-        <v>46234</v>
+        <v>46242</v>
       </c>
       <c r="I135" s="24" t="str">
         <f>IF(A135="","",IF(G135="Sim","Paga",IF(E135="","Sem vencimento",IF(E135&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22040,25 +22047,25 @@
     <row r="136">
       <c r="A136" s="33" t="inlineStr">
         <is>
-          <t>Roberta Lima</t>
+          <t>Lucas Lopes</t>
         </is>
       </c>
       <c r="B136" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C136" s="37" t="n">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="D136" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E136" s="37" t="n">
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="F136" s="38" t="n">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="G136" s="35" t="inlineStr">
         <is>
@@ -22066,7 +22073,7 @@
         </is>
       </c>
       <c r="H136" s="37" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="I136" s="24" t="str">
         <f>IF(A136="","",IF(G136="Sim","Paga",IF(E136="","Sem vencimento",IF(E136&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22100,25 +22107,25 @@
     <row r="137">
       <c r="A137" s="33" t="inlineStr">
         <is>
-          <t>Roberta Lima</t>
+          <t>Paulo Reis</t>
         </is>
       </c>
       <c r="B137" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C137" s="37" t="n">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="D137" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="37" t="n">
-        <v>46263</v>
+        <v>46247</v>
       </c>
       <c r="F137" s="38" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G137" s="35" t="inlineStr">
         <is>
@@ -22126,7 +22133,7 @@
         </is>
       </c>
       <c r="H137" s="37" t="n">
-        <v>46264</v>
+        <v>46248</v>
       </c>
       <c r="I137" s="24" t="str">
         <f>IF(A137="","",IF(G137="Sim","Paga",IF(E137="","Sem vencimento",IF(E137&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22160,7 +22167,7 @@
     <row r="138">
       <c r="A138" s="33" t="inlineStr">
         <is>
-          <t>Carlos Fernandes</t>
+          <t>Paulo Reis</t>
         </is>
       </c>
       <c r="B138" s="33" t="inlineStr">
@@ -22169,48 +22176,47 @@
         </is>
       </c>
       <c r="C138" s="37" t="n">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="D138" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="37" t="n">
-        <v>46239</v>
+        <v>2</v>
+      </c>
+      <c r="E138" s="37">
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="F138" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G138" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H138" s="37" t="n">
-        <v>46244</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H138" s="37" t="n"/>
       <c r="I138" s="24" t="str">
         <f>IF(A138="","",IF(G138="Sim","Paga",IF(E138="","Sem vencimento",IF(E138&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>Vencida</v>
       </c>
       <c r="J138" s="30">
         <f>IF(I138="Vencida",Config!$B$5-E138,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K138" s="30">
         <f>IF(I138="A vencer",E138-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L138" s="24">
+      <c r="L138" s="24" t="str">
         <f>IF(I138&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138))))</f>
-        <v/>
-      </c>
-      <c r="M138" s="23">
+        <v>1 a 6 dias</v>
+      </c>
+      <c r="M138" s="23" t="str">
         <f>IF(I138&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138))))</f>
-        <v/>
+        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
       </c>
       <c r="N138" s="39">
         <f>IF(I138="Vencida",F138*J138+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>380.00138</v>
       </c>
       <c r="O138" s="39">
         <f>IF(AND(I138="A vencer",K138&lt;=Config!$B$7),100000-K138-ROW()/100000,0)</f>
@@ -22220,7 +22226,7 @@
     <row r="139">
       <c r="A139" s="33" t="inlineStr">
         <is>
-          <t>Gustavo Ferreira</t>
+          <t>Cláudia Santos</t>
         </is>
       </c>
       <c r="B139" s="33" t="inlineStr">
@@ -22229,16 +22235,16 @@
         </is>
       </c>
       <c r="C139" s="37" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="D139" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E139" s="37" t="n">
-        <v>46240</v>
+        <v>46253</v>
       </c>
       <c r="F139" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G139" s="35" t="inlineStr">
         <is>
@@ -22246,7 +22252,7 @@
         </is>
       </c>
       <c r="H139" s="37" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="I139" s="24" t="str">
         <f>IF(A139="","",IF(G139="Sim","Paga",IF(E139="","Sem vencimento",IF(E139&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22289,47 +22295,48 @@
         </is>
       </c>
       <c r="C140" s="37" t="n">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="D140" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" s="37">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+        <v>1</v>
+      </c>
+      <c r="E140" s="37" t="n">
+        <v>46255</v>
       </c>
       <c r="F140" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G140" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H140" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H140" s="37" t="n">
+        <v>46258</v>
+      </c>
       <c r="I140" s="24" t="str">
         <f>IF(A140="","",IF(G140="Sim","Paga",IF(E140="","Sem vencimento",IF(E140&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J140" s="30">
         <f>IF(I140="Vencida",Config!$B$5-E140,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="K140" s="30">
         <f>IF(I140="A vencer",E140-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L140" s="24" t="str">
+      <c r="L140" s="24">
         <f>IF(I140&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J140)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J140))))</f>
-        <v>7 a 14 dias</v>
-      </c>
-      <c r="M140" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M140" s="23">
         <f>IF(I140&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J140)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J140))))</f>
-        <v>Mensagem da recepção perguntando se houve algum imprevisto e oferecendo uma nova data para o pagamento.</v>
+        <v/>
       </c>
       <c r="N140" s="39">
         <f>IF(I140="Vencida",F140*J140+ROW()/100000,0)</f>
-        <v>1710.0014</v>
+        <v>0</v>
       </c>
       <c r="O140" s="39">
         <f>IF(AND(I140="A vencer",K140&lt;=Config!$B$7),100000-K140-ROW()/100000,0)</f>
@@ -22339,7 +22346,7 @@
     <row r="141">
       <c r="A141" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Rafael Barros</t>
         </is>
       </c>
       <c r="B141" s="33" t="inlineStr">
@@ -22348,16 +22355,16 @@
         </is>
       </c>
       <c r="C141" s="37" t="n">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="D141" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E141" s="37" t="n">
-        <v>46246</v>
+        <v>46256</v>
       </c>
       <c r="F141" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G141" s="35" t="inlineStr">
         <is>
@@ -22365,7 +22372,7 @@
         </is>
       </c>
       <c r="H141" s="37" t="n">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="I141" s="24" t="str">
         <f>IF(A141="","",IF(G141="Sim","Paga",IF(E141="","Sem vencimento",IF(E141&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22399,25 +22406,25 @@
     <row r="142">
       <c r="A142" s="33" t="inlineStr">
         <is>
-          <t>Helena Moreira</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="B142" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C142" s="37" t="n">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="D142" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="37" t="n">
-        <v>46276</v>
+        <v>46257</v>
       </c>
       <c r="F142" s="38" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="G142" s="35" t="inlineStr">
         <is>
@@ -22425,7 +22432,7 @@
         </is>
       </c>
       <c r="H142" s="37" t="n">
-        <v>46276</v>
+        <v>46259</v>
       </c>
       <c r="I142" s="24" t="str">
         <f>IF(A142="","",IF(G142="Sim","Paga",IF(E142="","Sem vencimento",IF(E142&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22459,37 +22466,36 @@
     <row r="143">
       <c r="A143" s="33" t="inlineStr">
         <is>
-          <t>Lucas Lopes</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="B143" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C143" s="37" t="n">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="D143" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="37" t="n">
-        <v>46247</v>
+        <v>2</v>
+      </c>
+      <c r="E143" s="37">
+        <f>TODAY()+8</f>
+        <v>46287.0</v>
       </c>
       <c r="F143" s="38" t="n">
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="G143" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H143" s="37" t="n">
-        <v>46247</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H143" s="37" t="n"/>
       <c r="I143" s="24" t="str">
         <f>IF(A143="","",IF(G143="Sim","Paga",IF(E143="","Sem vencimento",IF(E143&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J143" s="30">
         <f>IF(I143="Vencida",Config!$B$5-E143,"")</f>
@@ -22497,7 +22503,7 @@
       </c>
       <c r="K143" s="30">
         <f>IF(I143="A vencer",E143-Config!$B$5,"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="L143" s="24">
         <f>IF(I143&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J143)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J143))))</f>
@@ -22513,13 +22519,13 @@
       </c>
       <c r="O143" s="39">
         <f>IF(AND(I143="A vencer",K143&lt;=Config!$B$7),100000-K143-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99991.99857</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="33" t="inlineStr">
         <is>
-          <t>Paulo Reis</t>
+          <t>Regina Duarte</t>
         </is>
       </c>
       <c r="B144" s="33" t="inlineStr">
@@ -22528,16 +22534,16 @@
         </is>
       </c>
       <c r="C144" s="37" t="n">
-        <v>46217</v>
+        <v>46230</v>
       </c>
       <c r="D144" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E144" s="37" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
       <c r="F144" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G144" s="35" t="inlineStr">
         <is>
@@ -22545,7 +22551,7 @@
         </is>
       </c>
       <c r="H144" s="37" t="n">
-        <v>46250</v>
+        <v>46261</v>
       </c>
       <c r="I144" s="24" t="str">
         <f>IF(A144="","",IF(G144="Sim","Paga",IF(E144="","Sem vencimento",IF(E144&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22579,56 +22585,57 @@
     <row r="145">
       <c r="A145" s="33" t="inlineStr">
         <is>
-          <t>Paulo Reis</t>
+          <t>Rodrigo Moreira</t>
         </is>
       </c>
       <c r="B145" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C145" s="37" t="n">
-        <v>46217</v>
+        <v>46230</v>
       </c>
       <c r="D145" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E145" s="37">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+        <v>1</v>
+      </c>
+      <c r="E145" s="37" t="n">
+        <v>46260</v>
       </c>
       <c r="F145" s="38" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="G145" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H145" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H145" s="37" t="n">
+        <v>46260</v>
+      </c>
       <c r="I145" s="24" t="str">
         <f>IF(A145="","",IF(G145="Sim","Paga",IF(E145="","Sem vencimento",IF(E145&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J145" s="30">
         <f>IF(I145="Vencida",Config!$B$5-E145,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="K145" s="30">
         <f>IF(I145="A vencer",E145-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L145" s="24" t="str">
+      <c r="L145" s="24">
         <f>IF(I145&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J145)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J145))))</f>
-        <v>1 a 6 dias</v>
-      </c>
-      <c r="M145" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M145" s="23">
         <f>IF(I145&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J145)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J145))))</f>
-        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
+        <v/>
       </c>
       <c r="N145" s="39">
         <f>IF(I145="Vencida",F145*J145+ROW()/100000,0)</f>
-        <v>380.00145</v>
+        <v>0</v>
       </c>
       <c r="O145" s="39">
         <f>IF(AND(I145="A vencer",K145&lt;=Config!$B$7),100000-K145-ROW()/100000,0)</f>
@@ -22638,37 +22645,36 @@
     <row r="146">
       <c r="A146" s="33" t="inlineStr">
         <is>
-          <t>Rafael Dias</t>
+          <t>Rodrigo Moreira</t>
         </is>
       </c>
       <c r="B146" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C146" s="37" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="D146" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" s="37" t="n">
-        <v>46253</v>
+        <v>2</v>
+      </c>
+      <c r="E146" s="37">
+        <f>TODAY()+11</f>
+        <v>46290.0</v>
       </c>
       <c r="F146" s="38" t="n">
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="G146" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H146" s="37" t="n">
-        <v>46258</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H146" s="37" t="n"/>
       <c r="I146" s="24" t="str">
         <f>IF(A146="","",IF(G146="Sim","Paga",IF(E146="","Sem vencimento",IF(E146&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J146" s="30">
         <f>IF(I146="Vencida",Config!$B$5-E146,"")</f>
@@ -22676,7 +22682,7 @@
       </c>
       <c r="K146" s="30">
         <f>IF(I146="A vencer",E146-Config!$B$5,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="L146" s="24">
         <f>IF(I146&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J146)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J146))))</f>
@@ -22692,31 +22698,31 @@
       </c>
       <c r="O146" s="39">
         <f>IF(AND(I146="A vencer",K146&lt;=Config!$B$7),100000-K146-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99988.99854</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Santos</t>
+          <t>Otávio Nascimento</t>
         </is>
       </c>
       <c r="B147" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="C147" s="37" t="n">
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="D147" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E147" s="37" t="n">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="F147" s="38" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="G147" s="35" t="inlineStr">
         <is>
@@ -22724,7 +22730,7 @@
         </is>
       </c>
       <c r="H147" s="37" t="n">
-        <v>46255</v>
+        <v>46266</v>
       </c>
       <c r="I147" s="24" t="str">
         <f>IF(A147="","",IF(G147="Sim","Paga",IF(E147="","Sem vencimento",IF(E147&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22758,25 +22764,25 @@
     <row r="148">
       <c r="A148" s="33" t="inlineStr">
         <is>
-          <t>Gustavo Ferreira</t>
+          <t>Rafael Pereira</t>
         </is>
       </c>
       <c r="B148" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C148" s="37" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="D148" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E148" s="37" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="F148" s="38" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="G148" s="35" t="inlineStr">
         <is>
@@ -22784,7 +22790,7 @@
         </is>
       </c>
       <c r="H148" s="37" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="I148" s="24" t="str">
         <f>IF(A148="","",IF(G148="Sim","Paga",IF(E148="","Sem vencimento",IF(E148&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22818,7 +22824,7 @@
     <row r="149">
       <c r="A149" s="33" t="inlineStr">
         <is>
-          <t>Márcia Duarte</t>
+          <t>Rafael Pereira</t>
         </is>
       </c>
       <c r="B149" s="33" t="inlineStr">
@@ -22827,28 +22833,27 @@
         </is>
       </c>
       <c r="C149" s="37" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="D149" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="37" t="n">
-        <v>46256</v>
+        <v>2</v>
+      </c>
+      <c r="E149" s="37">
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="F149" s="38" t="n">
         <v>200</v>
       </c>
       <c r="G149" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H149" s="37" t="n">
-        <v>46256</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H149" s="37" t="n"/>
       <c r="I149" s="24" t="str">
         <f>IF(A149="","",IF(G149="Sim","Paga",IF(E149="","Sem vencimento",IF(E149&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J149" s="30">
         <f>IF(I149="Vencida",Config!$B$5-E149,"")</f>
@@ -22856,7 +22861,7 @@
       </c>
       <c r="K149" s="30">
         <f>IF(I149="A vencer",E149-Config!$B$5,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="L149" s="24">
         <f>IF(I149&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J149)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J149))))</f>
@@ -22872,42 +22877,43 @@
       </c>
       <c r="O149" s="39">
         <f>IF(AND(I149="A vencer",K149&lt;=Config!$B$7),100000-K149-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99987.99851</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="33" t="inlineStr">
         <is>
-          <t>Márcia Duarte</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B150" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C150" s="37" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="D150" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E150" s="37">
-        <f>TODAY()+7</f>
-        <v>46286.0</v>
+        <v>1</v>
+      </c>
+      <c r="E150" s="37" t="n">
+        <v>46267</v>
       </c>
       <c r="F150" s="38" t="n">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="G150" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H150" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H150" s="37" t="n">
+        <v>46267</v>
+      </c>
       <c r="I150" s="24" t="str">
         <f>IF(A150="","",IF(G150="Sim","Paga",IF(E150="","Sem vencimento",IF(E150&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v>Paga</v>
       </c>
       <c r="J150" s="30">
         <f>IF(I150="Vencida",Config!$B$5-E150,"")</f>
@@ -22915,7 +22921,7 @@
       </c>
       <c r="K150" s="30">
         <f>IF(I150="A vencer",E150-Config!$B$5,"")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="L150" s="24">
         <f>IF(I150&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J150)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J150))))</f>
@@ -22931,31 +22937,31 @@
       </c>
       <c r="O150" s="39">
         <f>IF(AND(I150="A vencer",K150&lt;=Config!$B$7),100000-K150-ROW()/100000,0)</f>
-        <v>99992.9985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="33" t="inlineStr">
         <is>
-          <t>Rafael Barros</t>
+          <t>Isabela Xavier</t>
         </is>
       </c>
       <c r="B151" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C151" s="37" t="n">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="D151" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E151" s="37" t="n">
-        <v>46256</v>
+        <v>46268</v>
       </c>
       <c r="F151" s="38" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="G151" s="35" t="inlineStr">
         <is>
@@ -22963,7 +22969,7 @@
         </is>
       </c>
       <c r="H151" s="37" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="I151" s="24" t="str">
         <f>IF(A151="","",IF(G151="Sim","Paga",IF(E151="","Sem vencimento",IF(E151&lt;Config!$B$5,"Vencida","A vencer"))))</f>
@@ -22997,36 +23003,37 @@
     <row r="152">
       <c r="A152" s="33" t="inlineStr">
         <is>
-          <t>Rafael Barros</t>
+          <t>Roberta Lima</t>
         </is>
       </c>
       <c r="B152" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C152" s="37" t="n">
-        <v>46226</v>
+        <v>46240</v>
       </c>
       <c r="D152" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" s="37">
-        <f>TODAY()+7</f>
-        <v>46286.0</v>
+        <v>1</v>
+      </c>
+      <c r="E152" s="37" t="n">
+        <v>46270</v>
       </c>
       <c r="F152" s="38" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="G152" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H152" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H152" s="37" t="n">
+        <v>46272</v>
+      </c>
       <c r="I152" s="24" t="str">
         <f>IF(A152="","",IF(G152="Sim","Paga",IF(E152="","Sem vencimento",IF(E152&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v>Paga</v>
       </c>
       <c r="J152" s="30">
         <f>IF(I152="Vencida",Config!$B$5-E152,"")</f>
@@ -23034,7 +23041,7 @@
       </c>
       <c r="K152" s="30">
         <f>IF(I152="A vencer",E152-Config!$B$5,"")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="L152" s="24">
         <f>IF(I152&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J152)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J152))))</f>
@@ -23050,62 +23057,63 @@
       </c>
       <c r="O152" s="39">
         <f>IF(AND(I152="A vencer",K152&lt;=Config!$B$7),100000-K152-ROW()/100000,0)</f>
-        <v>99992.99848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="33" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Sérgio Martins</t>
         </is>
       </c>
       <c r="B153" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C153" s="37" t="n">
-        <v>46227</v>
+        <v>46244</v>
       </c>
       <c r="D153" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="37">
-        <f>TODAY()-22</f>
-        <v>46257.0</v>
+      <c r="E153" s="37" t="n">
+        <v>46274</v>
       </c>
       <c r="F153" s="38" t="n">
-        <v>450</v>
+        <v>190</v>
       </c>
       <c r="G153" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H153" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H153" s="37" t="n">
+        <v>46274</v>
+      </c>
       <c r="I153" s="24" t="str">
         <f>IF(A153="","",IF(G153="Sim","Paga",IF(E153="","Sem vencimento",IF(E153&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>Paga</v>
       </c>
       <c r="J153" s="30">
         <f>IF(I153="Vencida",Config!$B$5-E153,"")</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="K153" s="30">
         <f>IF(I153="A vencer",E153-Config!$B$5,"")</f>
         <v/>
       </c>
-      <c r="L153" s="24" t="str">
+      <c r="L153" s="24">
         <f>IF(I153&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J153)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J153))))</f>
-        <v>15 a 29 dias</v>
-      </c>
-      <c r="M153" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M153" s="23">
         <f>IF(I153&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J153)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J153))))</f>
-        <v>Ligação da recepção com o demonstrativo das parcelas em aberto e proposta de nova data ou divisão do valor.</v>
+        <v/>
       </c>
       <c r="N153" s="39">
         <f>IF(I153="Vencida",F153*J153+ROW()/100000,0)</f>
-        <v>9900.00153</v>
+        <v>0</v>
       </c>
       <c r="O153" s="39">
         <f>IF(AND(I153="A vencer",K153&lt;=Config!$B$7),100000-K153-ROW()/100000,0)</f>
@@ -23115,7 +23123,7 @@
     <row r="154">
       <c r="A154" s="33" t="inlineStr">
         <is>
-          <t>Regina Duarte</t>
+          <t>Sérgio Martins</t>
         </is>
       </c>
       <c r="B154" s="33" t="inlineStr">
@@ -23124,28 +23132,27 @@
         </is>
       </c>
       <c r="C154" s="37" t="n">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="D154" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" s="37" t="n">
-        <v>46260</v>
+        <v>2</v>
+      </c>
+      <c r="E154" s="37">
+        <f>TODAY()+25</f>
+        <v>46304.0</v>
       </c>
       <c r="F154" s="38" t="n">
         <v>190</v>
       </c>
       <c r="G154" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H154" s="37" t="n">
-        <v>46265</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H154" s="37" t="n"/>
       <c r="I154" s="24" t="str">
         <f>IF(A154="","",IF(G154="Sim","Paga",IF(E154="","Sem vencimento",IF(E154&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J154" s="30">
         <f>IF(I154="Vencida",Config!$B$5-E154,"")</f>
@@ -23153,7 +23160,7 @@
       </c>
       <c r="K154" s="30">
         <f>IF(I154="A vencer",E154-Config!$B$5,"")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="L154" s="24">
         <f>IF(I154&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J154)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J154))))</f>
@@ -23169,42 +23176,43 @@
       </c>
       <c r="O154" s="39">
         <f>IF(AND(I154="A vencer",K154&lt;=Config!$B$7),100000-K154-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99974.99846</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="33" t="inlineStr">
         <is>
-          <t>Regina Duarte</t>
+          <t>Fábio Gomes</t>
         </is>
       </c>
       <c r="B155" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C155" s="37" t="n">
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="D155" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E155" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+        <v>1</v>
+      </c>
+      <c r="E155" s="37" t="n">
+        <v>46275</v>
       </c>
       <c r="F155" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G155" s="35" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="H155" s="37" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H155" s="37" t="n">
+        <v>46276</v>
+      </c>
       <c r="I155" s="24" t="str">
         <f>IF(A155="","",IF(G155="Sim","Paga",IF(E155="","Sem vencimento",IF(E155&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v>Paga</v>
       </c>
       <c r="J155" s="30">
         <f>IF(I155="Vencida",Config!$B$5-E155,"")</f>
@@ -23212,7 +23220,7 @@
       </c>
       <c r="K155" s="30">
         <f>IF(I155="A vencer",E155-Config!$B$5,"")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="L155" s="24">
         <f>IF(I155&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J155)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J155))))</f>
@@ -23228,43 +23236,42 @@
       </c>
       <c r="O155" s="39">
         <f>IF(AND(I155="A vencer",K155&lt;=Config!$B$7),100000-K155-ROW()/100000,0)</f>
-        <v>99988.99845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="33" t="inlineStr">
         <is>
-          <t>Rodrigo Moreira</t>
+          <t>Fábio Gomes</t>
         </is>
       </c>
       <c r="B156" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C156" s="37" t="n">
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="D156" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="37" t="n">
-        <v>46260</v>
+        <v>2</v>
+      </c>
+      <c r="E156" s="37">
+        <f>TODAY()+26</f>
+        <v>46305.0</v>
       </c>
       <c r="F156" s="38" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G156" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H156" s="37" t="n">
-        <v>46263</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H156" s="37" t="n"/>
       <c r="I156" s="24" t="str">
         <f>IF(A156="","",IF(G156="Sim","Paga",IF(E156="","Sem vencimento",IF(E156&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J156" s="30">
         <f>IF(I156="Vencida",Config!$B$5-E156,"")</f>
@@ -23272,7 +23279,7 @@
       </c>
       <c r="K156" s="30">
         <f>IF(I156="A vencer",E156-Config!$B$5,"")</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="L156" s="24">
         <f>IF(I156&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J156)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J156))))</f>
@@ -23288,32 +23295,32 @@
       </c>
       <c r="O156" s="39">
         <f>IF(AND(I156="A vencer",K156&lt;=Config!$B$7),100000-K156-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99973.99844</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="33" t="inlineStr">
         <is>
-          <t>Rodrigo Moreira</t>
+          <t>Elaine Cardoso</t>
         </is>
       </c>
       <c r="B157" s="33" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>ECG</t>
         </is>
       </c>
       <c r="C157" s="37" t="n">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="D157" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="F157" s="38" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="G157" s="35" t="inlineStr">
         <is>
@@ -23323,67 +23330,66 @@
       <c r="H157" s="37" t="n"/>
       <c r="I157" s="24" t="str">
         <f>IF(A157="","",IF(G157="Sim","Paga",IF(E157="","Sem vencimento",IF(E157&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v>Vencida</v>
       </c>
       <c r="J157" s="30">
         <f>IF(I157="Vencida",Config!$B$5-E157,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K157" s="30">
         <f>IF(I157="A vencer",E157-Config!$B$5,"")</f>
-        <v>11</v>
-      </c>
-      <c r="L157" s="24">
+        <v/>
+      </c>
+      <c r="L157" s="24" t="str">
         <f>IF(I157&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157))))</f>
-        <v/>
-      </c>
-      <c r="M157" s="23">
+        <v>1 a 6 dias</v>
+      </c>
+      <c r="M157" s="23" t="str">
         <f>IF(I157&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157))))</f>
-        <v/>
+        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
       </c>
       <c r="N157" s="39">
         <f>IF(I157="Vencida",F157*J157+ROW()/100000,0)</f>
-        <v>0</v>
+        <v>130.00157</v>
       </c>
       <c r="O157" s="39">
         <f>IF(AND(I157="A vencer",K157&lt;=Config!$B$7),100000-K157-ROW()/100000,0)</f>
-        <v>99988.99843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="33" t="inlineStr">
         <is>
-          <t>Otávio Nascimento</t>
+          <t>Elaine Cardoso</t>
         </is>
       </c>
       <c r="B158" s="33" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C158" s="37" t="n">
-        <v>46231</v>
+        <v>46251</v>
       </c>
       <c r="D158" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E158" s="37" t="n">
-        <v>46261</v>
+      <c r="E158" s="37">
+        <f>TODAY()+2</f>
+        <v>46281.0</v>
       </c>
       <c r="F158" s="38" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="G158" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H158" s="37" t="n">
-        <v>46261</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H158" s="37" t="n"/>
       <c r="I158" s="24" t="str">
         <f>IF(A158="","",IF(G158="Sim","Paga",IF(E158="","Sem vencimento",IF(E158&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J158" s="30">
         <f>IF(I158="Vencida",Config!$B$5-E158,"")</f>
@@ -23391,7 +23397,7 @@
       </c>
       <c r="K158" s="30">
         <f>IF(I158="A vencer",E158-Config!$B$5,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="L158" s="24">
         <f>IF(I158&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J158)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J158))))</f>
@@ -23407,43 +23413,42 @@
       </c>
       <c r="O158" s="39">
         <f>IF(AND(I158="A vencer",K158&lt;=Config!$B$7),100000-K158-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99997.99842</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="33" t="inlineStr">
         <is>
-          <t>Rafael Pereira</t>
+          <t>Elaine Cardoso</t>
         </is>
       </c>
       <c r="B159" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C159" s="37" t="n">
-        <v>46231</v>
+        <v>46251</v>
       </c>
       <c r="D159" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" s="37" t="n">
-        <v>46261</v>
+        <v>2</v>
+      </c>
+      <c r="E159" s="37">
+        <f>TODAY()+32</f>
+        <v>46311.0</v>
       </c>
       <c r="F159" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G159" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H159" s="37" t="n">
-        <v>46266</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H159" s="37" t="n"/>
       <c r="I159" s="24" t="str">
         <f>IF(A159="","",IF(G159="Sim","Paga",IF(E159="","Sem vencimento",IF(E159&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J159" s="30">
         <f>IF(I159="Vencida",Config!$B$5-E159,"")</f>
@@ -23451,7 +23456,7 @@
       </c>
       <c r="K159" s="30">
         <f>IF(I159="A vencer",E159-Config!$B$5,"")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="L159" s="24">
         <f>IF(I159&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J159)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J159))))</f>
@@ -23473,37 +23478,36 @@
     <row r="160">
       <c r="A160" s="33" t="inlineStr">
         <is>
-          <t>Larissa Costa</t>
+          <t>Fábio Gomes</t>
         </is>
       </c>
       <c r="B160" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C160" s="37" t="n">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="D160" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E160" s="37" t="n">
-        <v>46267</v>
+      <c r="E160" s="37">
+        <f>TODAY()+3</f>
+        <v>46282.0</v>
       </c>
       <c r="F160" s="38" t="n">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="G160" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H160" s="37" t="n">
-        <v>46267</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H160" s="37" t="n"/>
       <c r="I160" s="24" t="str">
         <f>IF(A160="","",IF(G160="Sim","Paga",IF(E160="","Sem vencimento",IF(E160&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J160" s="30">
         <f>IF(I160="Vencida",Config!$B$5-E160,"")</f>
@@ -23511,7 +23515,7 @@
       </c>
       <c r="K160" s="30">
         <f>IF(I160="A vencer",E160-Config!$B$5,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="L160" s="24">
         <f>IF(I160&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J160)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J160))))</f>
@@ -23527,13 +23531,13 @@
       </c>
       <c r="O160" s="39">
         <f>IF(AND(I160="A vencer",K160&lt;=Config!$B$7),100000-K160-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99996.9984</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="33" t="inlineStr">
         <is>
-          <t>Larissa Costa</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="B161" s="33" t="inlineStr">
@@ -23542,17 +23546,17 @@
         </is>
       </c>
       <c r="C161" s="37" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="D161" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="37">
-        <f>TODAY()+18</f>
-        <v>46297.0</v>
+        <f>TODAY()+5</f>
+        <v>46284.0</v>
       </c>
       <c r="F161" s="38" t="n">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="G161" s="35" t="inlineStr">
         <is>
@@ -23570,7 +23574,7 @@
       </c>
       <c r="K161" s="30">
         <f>IF(I161="A vencer",E161-Config!$B$5,"")</f>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L161" s="24">
         <f>IF(I161&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J161)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J161))))</f>
@@ -23586,43 +23590,42 @@
       </c>
       <c r="O161" s="39">
         <f>IF(AND(I161="A vencer",K161&lt;=Config!$B$7),100000-K161-ROW()/100000,0)</f>
-        <v>99981.99839</v>
+        <v>99994.99839</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="33" t="inlineStr">
         <is>
-          <t>Isabela Xavier</t>
+          <t>Cláudia Santos</t>
         </is>
       </c>
       <c r="B162" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C162" s="37" t="n">
-        <v>46238</v>
+        <v>46258</v>
       </c>
       <c r="D162" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="37" t="n">
-        <v>46268</v>
+      <c r="E162" s="37">
+        <f>TODAY()+9</f>
+        <v>46288.0</v>
       </c>
       <c r="F162" s="38" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G162" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H162" s="37" t="n">
-        <v>46271</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H162" s="37" t="n"/>
       <c r="I162" s="24" t="str">
         <f>IF(A162="","",IF(G162="Sim","Paga",IF(E162="","Sem vencimento",IF(E162&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J162" s="30">
         <f>IF(I162="Vencida",Config!$B$5-E162,"")</f>
@@ -23630,7 +23633,7 @@
       </c>
       <c r="K162" s="30">
         <f>IF(I162="A vencer",E162-Config!$B$5,"")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="L162" s="24">
         <f>IF(I162&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J162)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J162))))</f>
@@ -23646,32 +23649,32 @@
       </c>
       <c r="O162" s="39">
         <f>IF(AND(I162="A vencer",K162&lt;=Config!$B$7),100000-K162-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99990.99838</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="33" t="inlineStr">
         <is>
-          <t>Roberta Lima</t>
+          <t>Sérgio Martins</t>
         </is>
       </c>
       <c r="B163" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C163" s="37" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="D163" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E163" s="37">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+        <f>TODAY()+11</f>
+        <v>46290.0</v>
       </c>
       <c r="F163" s="38" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G163" s="35" t="inlineStr">
         <is>
@@ -23681,37 +23684,37 @@
       <c r="H163" s="37" t="n"/>
       <c r="I163" s="24" t="str">
         <f>IF(A163="","",IF(G163="Sim","Paga",IF(E163="","Sem vencimento",IF(E163&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>A vencer</v>
       </c>
       <c r="J163" s="30">
         <f>IF(I163="Vencida",Config!$B$5-E163,"")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="K163" s="30">
         <f>IF(I163="A vencer",E163-Config!$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="L163" s="24" t="str">
+        <v>11</v>
+      </c>
+      <c r="L163" s="24">
         <f>IF(I163&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J163)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J163))))</f>
-        <v>7 a 14 dias</v>
-      </c>
-      <c r="M163" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M163" s="23">
         <f>IF(I163&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J163)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J163))))</f>
-        <v>Mensagem da recepção perguntando se houve algum imprevisto e oferecendo uma nova data para o pagamento.</v>
+        <v/>
       </c>
       <c r="N163" s="39">
         <f>IF(I163="Vencida",F163*J163+ROW()/100000,0)</f>
-        <v>3600.00163</v>
+        <v>0</v>
       </c>
       <c r="O163" s="39">
         <f>IF(AND(I163="A vencer",K163&lt;=Config!$B$7),100000-K163-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99988.99837</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="33" t="inlineStr">
         <is>
-          <t>Sérgio Martins</t>
+          <t>Gisele Ribeiro</t>
         </is>
       </c>
       <c r="B164" s="33" t="inlineStr">
@@ -23720,28 +23723,27 @@
         </is>
       </c>
       <c r="C164" s="37" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="D164" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="37" t="n">
-        <v>46274</v>
+      <c r="E164" s="37">
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="F164" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G164" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H164" s="37" t="n">
-        <v>46274</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H164" s="37" t="n"/>
       <c r="I164" s="24" t="str">
         <f>IF(A164="","",IF(G164="Sim","Paga",IF(E164="","Sem vencimento",IF(E164&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J164" s="30">
         <f>IF(I164="Vencida",Config!$B$5-E164,"")</f>
@@ -23749,7 +23751,7 @@
       </c>
       <c r="K164" s="30">
         <f>IF(I164="A vencer",E164-Config!$B$5,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="L164" s="24">
         <f>IF(I164&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J164)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J164))))</f>
@@ -23765,43 +23767,42 @@
       </c>
       <c r="O164" s="39">
         <f>IF(AND(I164="A vencer",K164&lt;=Config!$B$7),100000-K164-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99987.99836</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="33" t="inlineStr">
         <is>
-          <t>Fábio Gomes</t>
+          <t>Gisele Ribeiro</t>
         </is>
       </c>
       <c r="B165" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C165" s="37" t="n">
-        <v>46245</v>
+        <v>46261</v>
       </c>
       <c r="D165" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" s="37" t="n">
-        <v>46275</v>
+        <v>2</v>
+      </c>
+      <c r="E165" s="37">
+        <f>TODAY()+42</f>
+        <v>46321.0</v>
       </c>
       <c r="F165" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G165" s="35" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H165" s="37" t="n">
-        <v>46276</v>
-      </c>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="H165" s="37" t="n"/>
       <c r="I165" s="24" t="str">
         <f>IF(A165="","",IF(G165="Sim","Paga",IF(E165="","Sem vencimento",IF(E165&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Paga</v>
+        <v>A vencer</v>
       </c>
       <c r="J165" s="30">
         <f>IF(I165="Vencida",Config!$B$5-E165,"")</f>
@@ -23809,7 +23810,7 @@
       </c>
       <c r="K165" s="30">
         <f>IF(I165="A vencer",E165-Config!$B$5,"")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="L165" s="24">
         <f>IF(I165&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J165)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J165))))</f>
@@ -23831,26 +23832,26 @@
     <row r="166">
       <c r="A166" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="B166" s="33" t="inlineStr">
         <is>
-          <t>ECG</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C166" s="37" t="n">
-        <v>46248</v>
+        <v>46261</v>
       </c>
       <c r="D166" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E166" s="37">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="F166" s="38" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="G166" s="35" t="inlineStr">
         <is>
@@ -23860,56 +23861,56 @@
       <c r="H166" s="37" t="n"/>
       <c r="I166" s="24" t="str">
         <f>IF(A166="","",IF(G166="Sim","Paga",IF(E166="","Sem vencimento",IF(E166&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>Vencida</v>
+        <v>A vencer</v>
       </c>
       <c r="J166" s="30">
         <f>IF(I166="Vencida",Config!$B$5-E166,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="K166" s="30">
         <f>IF(I166="A vencer",E166-Config!$B$5,"")</f>
-        <v/>
-      </c>
-      <c r="L166" s="24" t="str">
+        <v>12</v>
+      </c>
+      <c r="L166" s="24">
         <f>IF(I166&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J166)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J166))))</f>
-        <v>1 a 6 dias</v>
-      </c>
-      <c r="M166" s="23" t="str">
+        <v/>
+      </c>
+      <c r="M166" s="23">
         <f>IF(I166&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J166)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J166))))</f>
-        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
+        <v/>
       </c>
       <c r="N166" s="39">
         <f>IF(I166="Vencida",F166*J166+ROW()/100000,0)</f>
-        <v>130.00166</v>
+        <v>0</v>
       </c>
       <c r="O166" s="39">
         <f>IF(AND(I166="A vencer",K166&lt;=Config!$B$7),100000-K166-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99987.99834</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="B167" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C167" s="37" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="D167" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="37">
-        <f>TODAY()+2</f>
-        <v>46281.0</v>
+        <f>TODAY()+42</f>
+        <v>46321.0</v>
       </c>
       <c r="F167" s="38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G167" s="35" t="inlineStr">
         <is>
@@ -23927,7 +23928,7 @@
       </c>
       <c r="K167" s="30">
         <f>IF(I167="A vencer",E167-Config!$B$5,"")</f>
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="L167" s="24">
         <f>IF(I167&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J167)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J167))))</f>
@@ -23943,32 +23944,32 @@
       </c>
       <c r="O167" s="39">
         <f>IF(AND(I167="A vencer",K167&lt;=Config!$B$7),100000-K167-ROW()/100000,0)</f>
-        <v>99997.99833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="33" t="inlineStr">
         <is>
-          <t>Elaine Cardoso</t>
+          <t>Renato Dias</t>
         </is>
       </c>
       <c r="B168" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="C168" s="37" t="n">
-        <v>46251</v>
+        <v>46261</v>
       </c>
       <c r="D168" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" s="37">
-        <f>TODAY()+32</f>
-        <v>46311.0</v>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="F168" s="38" t="n">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="G168" s="35" t="inlineStr">
         <is>
@@ -23986,7 +23987,7 @@
       </c>
       <c r="K168" s="30">
         <f>IF(I168="A vencer",E168-Config!$B$5,"")</f>
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="L168" s="24">
         <f>IF(I168&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J168)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J168))))</f>
@@ -24002,32 +24003,32 @@
       </c>
       <c r="O168" s="39">
         <f>IF(AND(I168="A vencer",K168&lt;=Config!$B$7),100000-K168-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99987.99832</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="33" t="inlineStr">
         <is>
-          <t>Fábio Gomes</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B169" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C169" s="37" t="n">
-        <v>46252</v>
+        <v>46268</v>
       </c>
       <c r="D169" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E169" s="37">
-        <f>TODAY()+3</f>
-        <v>46282.0</v>
+        <f>TODAY()+19</f>
+        <v>46298.0</v>
       </c>
       <c r="F169" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G169" s="35" t="inlineStr">
         <is>
@@ -24045,7 +24046,7 @@
       </c>
       <c r="K169" s="30">
         <f>IF(I169="A vencer",E169-Config!$B$5,"")</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L169" s="24">
         <f>IF(I169&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J169)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J169))))</f>
@@ -24061,13 +24062,13 @@
       </c>
       <c r="O169" s="39">
         <f>IF(AND(I169="A vencer",K169&lt;=Config!$B$7),100000-K169-ROW()/100000,0)</f>
-        <v>99996.99831</v>
+        <v>99980.99831</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="33" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B170" s="33" t="inlineStr">
@@ -24076,17 +24077,17 @@
         </is>
       </c>
       <c r="C170" s="37" t="n">
-        <v>46254</v>
+        <v>46268</v>
       </c>
       <c r="D170" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" s="37">
-        <f>TODAY()+5</f>
-        <v>46284.0</v>
+        <f>TODAY()+49</f>
+        <v>46328.0</v>
       </c>
       <c r="F170" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G170" s="35" t="inlineStr">
         <is>
@@ -24104,7 +24105,7 @@
       </c>
       <c r="K170" s="30">
         <f>IF(I170="A vencer",E170-Config!$B$5,"")</f>
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="L170" s="24">
         <f>IF(I170&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J170)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J170))))</f>
@@ -24120,32 +24121,32 @@
       </c>
       <c r="O170" s="39">
         <f>IF(AND(I170="A vencer",K170&lt;=Config!$B$7),100000-K170-ROW()/100000,0)</f>
-        <v>99994.9983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="33" t="inlineStr">
         <is>
-          <t>Cláudia Santos</t>
+          <t>Fernanda Freitas</t>
         </is>
       </c>
       <c r="B171" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C171" s="37" t="n">
-        <v>46258</v>
+        <v>46269</v>
       </c>
       <c r="D171" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E171" s="37">
-        <f>TODAY()+9</f>
-        <v>46288.0</v>
+        <f>TODAY()+20</f>
+        <v>46299.0</v>
       </c>
       <c r="F171" s="38" t="n">
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="G171" s="35" t="inlineStr">
         <is>
@@ -24163,7 +24164,7 @@
       </c>
       <c r="K171" s="30">
         <f>IF(I171="A vencer",E171-Config!$B$5,"")</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L171" s="24">
         <f>IF(I171&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J171)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J171))))</f>
@@ -24179,32 +24180,32 @@
       </c>
       <c r="O171" s="39">
         <f>IF(AND(I171="A vencer",K171&lt;=Config!$B$7),100000-K171-ROW()/100000,0)</f>
-        <v>99990.99829</v>
+        <v>99979.99829</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="33" t="inlineStr">
         <is>
-          <t>Sérgio Martins</t>
+          <t>Fernanda Freitas</t>
         </is>
       </c>
       <c r="B172" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="C172" s="37" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="D172" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+        <f>TODAY()+50</f>
+        <v>46329.0</v>
       </c>
       <c r="F172" s="38" t="n">
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="G172" s="35" t="inlineStr">
         <is>
@@ -24222,7 +24223,7 @@
       </c>
       <c r="K172" s="30">
         <f>IF(I172="A vencer",E172-Config!$B$5,"")</f>
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="L172" s="24">
         <f>IF(I172&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J172)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J172))))</f>
@@ -24238,13 +24239,13 @@
       </c>
       <c r="O172" s="39">
         <f>IF(AND(I172="A vencer",K172&lt;=Config!$B$7),100000-K172-ROW()/100000,0)</f>
-        <v>99988.99828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="33" t="inlineStr">
         <is>
-          <t>Gisele Ribeiro</t>
+          <t>Ana Costa</t>
         </is>
       </c>
       <c r="B173" s="33" t="inlineStr">
@@ -24253,17 +24254,17 @@
         </is>
       </c>
       <c r="C173" s="37" t="n">
-        <v>46261</v>
+        <v>46274</v>
       </c>
       <c r="D173" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E173" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+        <f>TODAY()+25</f>
+        <v>46304.0</v>
       </c>
       <c r="F173" s="38" t="n">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="G173" s="35" t="inlineStr">
         <is>
@@ -24281,7 +24282,7 @@
       </c>
       <c r="K173" s="30">
         <f>IF(I173="A vencer",E173-Config!$B$5,"")</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L173" s="24">
         <f>IF(I173&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J173)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J173))))</f>
@@ -24297,32 +24298,32 @@
       </c>
       <c r="O173" s="39">
         <f>IF(AND(I173="A vencer",K173&lt;=Config!$B$7),100000-K173-ROW()/100000,0)</f>
-        <v>99987.99827</v>
+        <v>99974.99827</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="33" t="inlineStr">
         <is>
-          <t>Renato Dias</t>
+          <t>Ana Costa</t>
         </is>
       </c>
       <c r="B174" s="33" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C174" s="37" t="n">
-        <v>46261</v>
+        <v>46274</v>
       </c>
       <c r="D174" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+        <f>TODAY()+55</f>
+        <v>46334.0</v>
       </c>
       <c r="F174" s="38" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G174" s="35" t="inlineStr">
         <is>
@@ -24340,7 +24341,7 @@
       </c>
       <c r="K174" s="30">
         <f>IF(I174="A vencer",E174-Config!$B$5,"")</f>
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="L174" s="24">
         <f>IF(I174&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J174)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J174))))</f>
@@ -24356,32 +24357,32 @@
       </c>
       <c r="O174" s="39">
         <f>IF(AND(I174="A vencer",K174&lt;=Config!$B$7),100000-K174-ROW()/100000,0)</f>
-        <v>99987.99826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="33" t="inlineStr">
         <is>
-          <t>Renato Dias</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B175" s="33" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C175" s="37" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D175" s="35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" s="37">
-        <f>TODAY()+42</f>
-        <v>46321.0</v>
+        <f>TODAY()+26</f>
+        <v>46305.0</v>
       </c>
       <c r="F175" s="38" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G175" s="35" t="inlineStr">
         <is>
@@ -24399,7 +24400,7 @@
       </c>
       <c r="K175" s="30">
         <f>IF(I175="A vencer",E175-Config!$B$5,"")</f>
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L175" s="24">
         <f>IF(I175&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J175)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J175))))</f>
@@ -24415,32 +24416,32 @@
       </c>
       <c r="O175" s="39">
         <f>IF(AND(I175="A vencer",K175&lt;=Config!$B$7),100000-K175-ROW()/100000,0)</f>
-        <v>0</v>
+        <v>99973.99825</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="33" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Larissa Costa</t>
         </is>
       </c>
       <c r="B176" s="33" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Consulta</t>
         </is>
       </c>
       <c r="C176" s="37" t="n">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="D176" s="35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+        <f>TODAY()+56</f>
+        <v>46335.0</v>
       </c>
       <c r="F176" s="38" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="G176" s="35" t="inlineStr">
         <is>
@@ -24458,7 +24459,7 @@
       </c>
       <c r="K176" s="30">
         <f>IF(I176="A vencer",E176-Config!$B$5,"")</f>
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="L176" s="24">
         <f>IF(I176&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J176)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J176))))</f>
@@ -24474,32 +24475,32 @@
       </c>
       <c r="O176" s="39">
         <f>IF(AND(I176="A vencer",K176&lt;=Config!$B$7),100000-K176-ROW()/100000,0)</f>
-        <v>99987.99824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="33" t="inlineStr">
         <is>
-          <t>Larissa Costa</t>
+          <t>Tatiana Macedo</t>
         </is>
       </c>
       <c r="B177" s="33" t="inlineStr">
         <is>
-          <t>Consulta</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="C177" s="37" t="n">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="D177" s="35" t="n">
         <v>1</v>
       </c>
       <c r="E177" s="37">
-        <f>TODAY()+19</f>
-        <v>46298.0</v>
+        <f>TODAY()+26</f>
+        <v>46305.0</v>
       </c>
       <c r="F177" s="38" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="G177" s="35" t="inlineStr">
         <is>
@@ -24517,7 +24518,7 @@
       </c>
       <c r="K177" s="30">
         <f>IF(I177="A vencer",E177-Config!$B$5,"")</f>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L177" s="24">
         <f>IF(I177&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J177)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J177))))</f>
@@ -24533,42 +24534,21 @@
       </c>
       <c r="O177" s="39">
         <f>IF(AND(I177="A vencer",K177&lt;=Config!$B$7),100000-K177-ROW()/100000,0)</f>
-        <v>99980.99823</v>
+        <v>99973.99823</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="33" t="inlineStr">
-        <is>
-          <t>Fernanda Freitas</t>
-        </is>
-      </c>
-      <c r="B178" s="33" t="inlineStr">
-        <is>
-          <t>Teste ergométrico</t>
-        </is>
-      </c>
-      <c r="C178" s="37" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D178" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="37">
-        <f>TODAY()+20</f>
-        <v>46299.0</v>
-      </c>
-      <c r="F178" s="38" t="n">
-        <v>450</v>
-      </c>
-      <c r="G178" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A178" s="33" t="n"/>
+      <c r="B178" s="33" t="n"/>
+      <c r="C178" s="37" t="n"/>
+      <c r="D178" s="35" t="n"/>
+      <c r="E178" s="37" t="n"/>
+      <c r="F178" s="38" t="n"/>
+      <c r="G178" s="35" t="n"/>
       <c r="H178" s="37" t="n"/>
-      <c r="I178" s="24" t="str">
+      <c r="I178" s="24">
         <f>IF(A178="","",IF(G178="Sim","Paga",IF(E178="","Sem vencimento",IF(E178&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J178" s="30">
         <f>IF(I178="Vencida",Config!$B$5-E178,"")</f>
@@ -24576,7 +24556,7 @@
       </c>
       <c r="K178" s="30">
         <f>IF(I178="A vencer",E178-Config!$B$5,"")</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="L178" s="24">
         <f>IF(I178&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J178)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J178))))</f>
@@ -24592,42 +24572,21 @@
       </c>
       <c r="O178" s="39">
         <f>IF(AND(I178="A vencer",K178&lt;=Config!$B$7),100000-K178-ROW()/100000,0)</f>
-        <v>99979.99822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="33" t="inlineStr">
-        <is>
-          <t>Ana Costa</t>
-        </is>
-      </c>
-      <c r="B179" s="33" t="inlineStr">
-        <is>
-          <t>Consulta</t>
-        </is>
-      </c>
-      <c r="C179" s="37" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D179" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" s="37">
-        <f>TODAY()+25</f>
-        <v>46304.0</v>
-      </c>
-      <c r="F179" s="38" t="n">
-        <v>190</v>
-      </c>
-      <c r="G179" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A179" s="33" t="n"/>
+      <c r="B179" s="33" t="n"/>
+      <c r="C179" s="37" t="n"/>
+      <c r="D179" s="35" t="n"/>
+      <c r="E179" s="37" t="n"/>
+      <c r="F179" s="38" t="n"/>
+      <c r="G179" s="35" t="n"/>
       <c r="H179" s="37" t="n"/>
-      <c r="I179" s="24" t="str">
+      <c r="I179" s="24">
         <f>IF(A179="","",IF(G179="Sim","Paga",IF(E179="","Sem vencimento",IF(E179&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J179" s="30">
         <f>IF(I179="Vencida",Config!$B$5-E179,"")</f>
@@ -24635,7 +24594,7 @@
       </c>
       <c r="K179" s="30">
         <f>IF(I179="A vencer",E179-Config!$B$5,"")</f>
-        <v>25</v>
+        <v/>
       </c>
       <c r="L179" s="24">
         <f>IF(I179&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J179)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J179))))</f>
@@ -24651,42 +24610,21 @@
       </c>
       <c r="O179" s="39">
         <f>IF(AND(I179="A vencer",K179&lt;=Config!$B$7),100000-K179-ROW()/100000,0)</f>
-        <v>99974.99821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="33" t="inlineStr">
-        <is>
-          <t>Ana Costa</t>
-        </is>
-      </c>
-      <c r="B180" s="33" t="inlineStr">
-        <is>
-          <t>Consulta</t>
-        </is>
-      </c>
-      <c r="C180" s="37" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D180" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E180" s="37">
-        <f>TODAY()+55</f>
-        <v>46334.0</v>
-      </c>
-      <c r="F180" s="38" t="n">
-        <v>190</v>
-      </c>
-      <c r="G180" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A180" s="33" t="n"/>
+      <c r="B180" s="33" t="n"/>
+      <c r="C180" s="37" t="n"/>
+      <c r="D180" s="35" t="n"/>
+      <c r="E180" s="37" t="n"/>
+      <c r="F180" s="38" t="n"/>
+      <c r="G180" s="35" t="n"/>
       <c r="H180" s="37" t="n"/>
-      <c r="I180" s="24" t="str">
+      <c r="I180" s="24">
         <f>IF(A180="","",IF(G180="Sim","Paga",IF(E180="","Sem vencimento",IF(E180&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J180" s="30">
         <f>IF(I180="Vencida",Config!$B$5-E180,"")</f>
@@ -24694,7 +24632,7 @@
       </c>
       <c r="K180" s="30">
         <f>IF(I180="A vencer",E180-Config!$B$5,"")</f>
-        <v>55</v>
+        <v/>
       </c>
       <c r="L180" s="24">
         <f>IF(I180&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J180)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J180))))</f>
@@ -24714,38 +24652,17 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="33" t="inlineStr">
-        <is>
-          <t>Larissa Costa</t>
-        </is>
-      </c>
-      <c r="B181" s="33" t="inlineStr">
-        <is>
-          <t>Consulta</t>
-        </is>
-      </c>
-      <c r="C181" s="37" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D181" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
-      </c>
-      <c r="F181" s="38" t="n">
-        <v>190</v>
-      </c>
-      <c r="G181" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A181" s="33" t="n"/>
+      <c r="B181" s="33" t="n"/>
+      <c r="C181" s="37" t="n"/>
+      <c r="D181" s="35" t="n"/>
+      <c r="E181" s="37" t="n"/>
+      <c r="F181" s="38" t="n"/>
+      <c r="G181" s="35" t="n"/>
       <c r="H181" s="37" t="n"/>
-      <c r="I181" s="24" t="str">
+      <c r="I181" s="24">
         <f>IF(A181="","",IF(G181="Sim","Paga",IF(E181="","Sem vencimento",IF(E181&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J181" s="30">
         <f>IF(I181="Vencida",Config!$B$5-E181,"")</f>
@@ -24753,7 +24670,7 @@
       </c>
       <c r="K181" s="30">
         <f>IF(I181="A vencer",E181-Config!$B$5,"")</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="L181" s="24">
         <f>IF(I181&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J181)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J181))))</f>
@@ -24769,42 +24686,21 @@
       </c>
       <c r="O181" s="39">
         <f>IF(AND(I181="A vencer",K181&lt;=Config!$B$7),100000-K181-ROW()/100000,0)</f>
-        <v>99973.99819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="33" t="inlineStr">
-        <is>
-          <t>Larissa Costa</t>
-        </is>
-      </c>
-      <c r="B182" s="33" t="inlineStr">
-        <is>
-          <t>Consulta</t>
-        </is>
-      </c>
-      <c r="C182" s="37" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D182" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E182" s="37">
-        <f>TODAY()+56</f>
-        <v>46335.0</v>
-      </c>
-      <c r="F182" s="38" t="n">
-        <v>190</v>
-      </c>
-      <c r="G182" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A182" s="33" t="n"/>
+      <c r="B182" s="33" t="n"/>
+      <c r="C182" s="37" t="n"/>
+      <c r="D182" s="35" t="n"/>
+      <c r="E182" s="37" t="n"/>
+      <c r="F182" s="38" t="n"/>
+      <c r="G182" s="35" t="n"/>
       <c r="H182" s="37" t="n"/>
-      <c r="I182" s="24" t="str">
+      <c r="I182" s="24">
         <f>IF(A182="","",IF(G182="Sim","Paga",IF(E182="","Sem vencimento",IF(E182&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J182" s="30">
         <f>IF(I182="Vencida",Config!$B$5-E182,"")</f>
@@ -24812,7 +24708,7 @@
       </c>
       <c r="K182" s="30">
         <f>IF(I182="A vencer",E182-Config!$B$5,"")</f>
-        <v>56</v>
+        <v/>
       </c>
       <c r="L182" s="24">
         <f>IF(I182&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J182)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J182))))</f>
@@ -24832,38 +24728,17 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="33" t="inlineStr">
-        <is>
-          <t>Tatiana Macedo</t>
-        </is>
-      </c>
-      <c r="B183" s="33" t="inlineStr">
-        <is>
-          <t>Avaliação endócrina</t>
-        </is>
-      </c>
-      <c r="C183" s="37" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D183" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
-      </c>
-      <c r="F183" s="38" t="n">
-        <v>200</v>
-      </c>
-      <c r="G183" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A183" s="33" t="n"/>
+      <c r="B183" s="33" t="n"/>
+      <c r="C183" s="37" t="n"/>
+      <c r="D183" s="35" t="n"/>
+      <c r="E183" s="37" t="n"/>
+      <c r="F183" s="38" t="n"/>
+      <c r="G183" s="35" t="n"/>
       <c r="H183" s="37" t="n"/>
-      <c r="I183" s="24" t="str">
+      <c r="I183" s="24">
         <f>IF(A183="","",IF(G183="Sim","Paga",IF(E183="","Sem vencimento",IF(E183&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J183" s="30">
         <f>IF(I183="Vencida",Config!$B$5-E183,"")</f>
@@ -24871,7 +24746,7 @@
       </c>
       <c r="K183" s="30">
         <f>IF(I183="A vencer",E183-Config!$B$5,"")</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="L183" s="24">
         <f>IF(I183&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J183)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J183))))</f>
@@ -24887,42 +24762,21 @@
       </c>
       <c r="O183" s="39">
         <f>IF(AND(I183="A vencer",K183&lt;=Config!$B$7),100000-K183-ROW()/100000,0)</f>
-        <v>99973.99817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="33" t="inlineStr">
-        <is>
-          <t>Tatiana Macedo</t>
-        </is>
-      </c>
-      <c r="B184" s="33" t="inlineStr">
-        <is>
-          <t>Avaliação endócrina</t>
-        </is>
-      </c>
-      <c r="C184" s="37" t="n">
-        <v>46275</v>
-      </c>
-      <c r="D184" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E184" s="37">
-        <f>TODAY()+56</f>
-        <v>46335.0</v>
-      </c>
-      <c r="F184" s="38" t="n">
-        <v>200</v>
-      </c>
-      <c r="G184" s="35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
+      <c r="A184" s="33" t="n"/>
+      <c r="B184" s="33" t="n"/>
+      <c r="C184" s="37" t="n"/>
+      <c r="D184" s="35" t="n"/>
+      <c r="E184" s="37" t="n"/>
+      <c r="F184" s="38" t="n"/>
+      <c r="G184" s="35" t="n"/>
       <c r="H184" s="37" t="n"/>
-      <c r="I184" s="24" t="str">
+      <c r="I184" s="24">
         <f>IF(A184="","",IF(G184="Sim","Paga",IF(E184="","Sem vencimento",IF(E184&lt;Config!$B$5,"Vencida","A vencer"))))</f>
-        <v>A vencer</v>
+        <v/>
       </c>
       <c r="J184" s="30">
         <f>IF(I184="Vencida",Config!$B$5-E184,"")</f>
@@ -24930,7 +24784,7 @@
       </c>
       <c r="K184" s="30">
         <f>IF(I184="A vencer",E184-Config!$B$5,"")</f>
-        <v>56</v>
+        <v/>
       </c>
       <c r="L184" s="24">
         <f>IF(I184&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J184)=0,"Antes da régua",INDEX(Config!$C$10:$C$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J184))))</f>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E11" s="27" t="str">
         <f>IF(Config!$C$10="","",Config!$B$10)</f>
-        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
+        <v>Lembrete gentil por WhatsApp: confirmar se o Pix chegou e reenviar o link de pagamento, se preciso.</v>
       </c>
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="21" t="n"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</t>
+          <t>Lembrete gentil por WhatsApp: confirmar se o Pix chegou e reenviar o link de pagamento, se preciso.</t>
         </is>
       </c>
       <c r="C10" s="24" t="str">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="M138" s="23" t="str">
         <f>IF(I138&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J138))))</f>
-        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
+        <v>Lembrete gentil por WhatsApp: confirmar se o Pix chegou e reenviar o link de pagamento, se preciso.</v>
       </c>
       <c r="N138" s="39">
         <f>IF(I138="Vencida",F138*J138+ROW()/100000,0)</f>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="M157" s="23" t="str">
         <f>IF(I157&lt;&gt;"Vencida","",IF(COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157)=0,"Aguardar: ainda não chegou ao primeiro passo da régua.",INDEX(Config!$B$10:$B$13,COUNTIF(Config!$A$10:$A$13,"&lt;="&amp;J157))))</f>
-        <v>Lembrete gentil por WhatsApp: confirmar se o Pix ou o boleto chegou e reenviar, se preciso.</v>
+        <v>Lembrete gentil por WhatsApp: confirmar se o Pix chegou e reenviar o link de pagamento, se preciso.</v>
       </c>
       <c r="N157" s="39">
         <f>IF(I157="Vencida",F157*J157+ROW()/100000,0)</f>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -2296,7 +2296,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Regra que vale mais que a régua: quem tem parcela vencida em aberto não combina novo pagamento a prazo. O próximo atendimento é à vista (Pix, dinheiro ou cartão) ou fica para depois de acertar o que está em atraso — sem constrangimento e em particular. No exemplo do kit, nenhum paciente com parcela vencida recebeu crédito novo, e o mesmo vale para orçamento aprovado a prazo (planilha 15).</t>
+          <t>Regra que vale mais que a régua: quem tem parcela vencida em aberto não combina novo parcelamento. O atendimento acontece normalmente; o que muda é a forma de pagamento, que passa a ser à vista (Pix, dinheiro ou cartão), combinada em particular e sem constrangimento. Atendimento nunca é condicionado a pagamento. No exemplo do kit, nenhum paciente com parcela vencida recebeu crédito novo, e o mesmo vale para orçamento aprovado a prazo (planilha 15).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -23,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -249,19 +250,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -279,7 +280,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,7 +290,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,7 +303,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,11 +314,11 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -844,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1017,17 +1018,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2181,9 +2194,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="34">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="34" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -14573,9 +14585,8 @@
       <c r="D11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="37">
-        <f>TODAY()-214</f>
-        <v>46065.0</v>
+      <c r="E11" s="37" t="n">
+        <v>46065</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>200</v>
@@ -15292,9 +15303,8 @@
       <c r="D23" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="37">
-        <f>TODAY()-185</f>
-        <v>46094.0</v>
+      <c r="E23" s="37" t="n">
+        <v>46094</v>
       </c>
       <c r="F23" s="38" t="n">
         <v>190</v>
@@ -16371,9 +16381,8 @@
       <c r="D41" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="37">
-        <f>TODAY()-158</f>
-        <v>46121.0</v>
+      <c r="E41" s="37" t="n">
+        <v>46121</v>
       </c>
       <c r="F41" s="38" t="n">
         <v>400</v>
@@ -16670,9 +16679,8 @@
       <c r="D46" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="37">
-        <f>TODAY()-119</f>
-        <v>46160.0</v>
+      <c r="E46" s="37" t="n">
+        <v>46160</v>
       </c>
       <c r="F46" s="38" t="n">
         <v>190</v>
@@ -16849,9 +16857,8 @@
       <c r="D49" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="37">
-        <f>TODAY()-114</f>
-        <v>46165.0</v>
+      <c r="E49" s="37" t="n">
+        <v>46165</v>
       </c>
       <c r="F49" s="38" t="n">
         <v>190</v>
@@ -17388,9 +17395,8 @@
       <c r="D58" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="37">
-        <f>TODAY()-130</f>
-        <v>46149.0</v>
+      <c r="E58" s="37" t="n">
+        <v>46149</v>
       </c>
       <c r="F58" s="38" t="n">
         <v>400</v>
@@ -19367,9 +19373,8 @@
       <c r="D91" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="37">
-        <f>TODAY()-93</f>
-        <v>46186.0</v>
+      <c r="E91" s="37" t="n">
+        <v>46186</v>
       </c>
       <c r="F91" s="38" t="n">
         <v>380</v>
@@ -19846,9 +19851,8 @@
       <c r="D99" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="37">
-        <f>TODAY()-87</f>
-        <v>46192.0</v>
+      <c r="E99" s="37" t="n">
+        <v>46192</v>
       </c>
       <c r="F99" s="38" t="n">
         <v>380</v>
@@ -20085,9 +20089,8 @@
       <c r="D103" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="37">
-        <f>TODAY()-79</f>
-        <v>46200.0</v>
+      <c r="E103" s="37" t="n">
+        <v>46200</v>
       </c>
       <c r="F103" s="38" t="n">
         <v>380</v>
@@ -20864,9 +20867,8 @@
       <c r="D116" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E116" s="37">
-        <f>TODAY()-31</f>
-        <v>46248.0</v>
+      <c r="E116" s="37" t="n">
+        <v>46248</v>
       </c>
       <c r="F116" s="38" t="n">
         <v>175</v>
@@ -21343,9 +21345,8 @@
       <c r="D124" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E124" s="37">
-        <f>TODAY()-54</f>
-        <v>46225.0</v>
+      <c r="E124" s="37" t="n">
+        <v>46225</v>
       </c>
       <c r="F124" s="38" t="n">
         <v>380</v>
@@ -21882,9 +21883,8 @@
       <c r="D133" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E133" s="37">
-        <f>TODAY()-40</f>
-        <v>46239.0</v>
+      <c r="E133" s="37" t="n">
+        <v>46239</v>
       </c>
       <c r="F133" s="38" t="n">
         <v>190</v>
@@ -22181,9 +22181,8 @@
       <c r="D138" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="37">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="E138" s="37" t="n">
+        <v>46277</v>
       </c>
       <c r="F138" s="38" t="n">
         <v>190</v>
@@ -22480,9 +22479,8 @@
       <c r="D143" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="37">
-        <f>TODAY()+8</f>
-        <v>46287.0</v>
+      <c r="E143" s="37" t="n">
+        <v>46287</v>
       </c>
       <c r="F143" s="38" t="n">
         <v>225</v>
@@ -22659,9 +22657,8 @@
       <c r="D146" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E146" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+      <c r="E146" s="37" t="n">
+        <v>46290</v>
       </c>
       <c r="F146" s="38" t="n">
         <v>225</v>
@@ -22838,9 +22835,8 @@
       <c r="D149" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E149" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+      <c r="E149" s="37" t="n">
+        <v>46291</v>
       </c>
       <c r="F149" s="38" t="n">
         <v>200</v>
@@ -23137,9 +23133,8 @@
       <c r="D154" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E154" s="37">
-        <f>TODAY()+25</f>
-        <v>46304.0</v>
+      <c r="E154" s="37" t="n">
+        <v>46304</v>
       </c>
       <c r="F154" s="38" t="n">
         <v>190</v>
@@ -23256,9 +23251,8 @@
       <c r="D156" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E156" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
+      <c r="E156" s="37" t="n">
+        <v>46305</v>
       </c>
       <c r="F156" s="38" t="n">
         <v>200</v>
@@ -23315,9 +23309,8 @@
       <c r="D157" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E157" s="37">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+      <c r="E157" s="37" t="n">
+        <v>46278</v>
       </c>
       <c r="F157" s="38" t="n">
         <v>130</v>
@@ -23374,9 +23367,8 @@
       <c r="D158" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E158" s="37">
-        <f>TODAY()+2</f>
-        <v>46281.0</v>
+      <c r="E158" s="37" t="n">
+        <v>46281</v>
       </c>
       <c r="F158" s="38" t="n">
         <v>190</v>
@@ -23433,9 +23425,8 @@
       <c r="D159" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E159" s="37">
-        <f>TODAY()+32</f>
-        <v>46311.0</v>
+      <c r="E159" s="37" t="n">
+        <v>46311</v>
       </c>
       <c r="F159" s="38" t="n">
         <v>190</v>
@@ -23492,9 +23483,8 @@
       <c r="D160" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E160" s="37">
-        <f>TODAY()+3</f>
-        <v>46282.0</v>
+      <c r="E160" s="37" t="n">
+        <v>46282</v>
       </c>
       <c r="F160" s="38" t="n">
         <v>400</v>
@@ -23551,9 +23541,8 @@
       <c r="D161" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E161" s="37">
-        <f>TODAY()+5</f>
-        <v>46284.0</v>
+      <c r="E161" s="37" t="n">
+        <v>46284</v>
       </c>
       <c r="F161" s="38" t="n">
         <v>380</v>
@@ -23610,9 +23599,8 @@
       <c r="D162" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="37">
-        <f>TODAY()+9</f>
-        <v>46288.0</v>
+      <c r="E162" s="37" t="n">
+        <v>46288</v>
       </c>
       <c r="F162" s="38" t="n">
         <v>380</v>
@@ -23669,9 +23657,8 @@
       <c r="D163" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="37">
-        <f>TODAY()+11</f>
-        <v>46290.0</v>
+      <c r="E163" s="37" t="n">
+        <v>46290</v>
       </c>
       <c r="F163" s="38" t="n">
         <v>380</v>
@@ -23728,9 +23715,8 @@
       <c r="D164" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+      <c r="E164" s="37" t="n">
+        <v>46291</v>
       </c>
       <c r="F164" s="38" t="n">
         <v>190</v>
@@ -23787,9 +23773,8 @@
       <c r="D165" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E165" s="37">
-        <f>TODAY()+42</f>
-        <v>46321.0</v>
+      <c r="E165" s="37" t="n">
+        <v>46321</v>
       </c>
       <c r="F165" s="38" t="n">
         <v>190</v>
@@ -23846,9 +23831,8 @@
       <c r="D166" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E166" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+      <c r="E166" s="37" t="n">
+        <v>46291</v>
       </c>
       <c r="F166" s="38" t="n">
         <v>200</v>
@@ -23905,9 +23889,8 @@
       <c r="D167" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E167" s="37">
-        <f>TODAY()+42</f>
-        <v>46321.0</v>
+      <c r="E167" s="37" t="n">
+        <v>46321</v>
       </c>
       <c r="F167" s="38" t="n">
         <v>200</v>
@@ -23964,9 +23947,8 @@
       <c r="D168" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E168" s="37">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+      <c r="E168" s="37" t="n">
+        <v>46291</v>
       </c>
       <c r="F168" s="38" t="n">
         <v>350</v>
@@ -24023,9 +24005,8 @@
       <c r="D169" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="37">
-        <f>TODAY()+19</f>
-        <v>46298.0</v>
+      <c r="E169" s="37" t="n">
+        <v>46298</v>
       </c>
       <c r="F169" s="38" t="n">
         <v>190</v>
@@ -24082,9 +24063,8 @@
       <c r="D170" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E170" s="37">
-        <f>TODAY()+49</f>
-        <v>46328.0</v>
+      <c r="E170" s="37" t="n">
+        <v>46328</v>
       </c>
       <c r="F170" s="38" t="n">
         <v>190</v>
@@ -24141,9 +24121,8 @@
       <c r="D171" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E171" s="37">
-        <f>TODAY()+20</f>
-        <v>46299.0</v>
+      <c r="E171" s="37" t="n">
+        <v>46299</v>
       </c>
       <c r="F171" s="38" t="n">
         <v>225</v>
@@ -24200,9 +24179,8 @@
       <c r="D172" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E172" s="37">
-        <f>TODAY()+50</f>
-        <v>46329.0</v>
+      <c r="E172" s="37" t="n">
+        <v>46329</v>
       </c>
       <c r="F172" s="38" t="n">
         <v>225</v>
@@ -24259,9 +24237,8 @@
       <c r="D173" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E173" s="37">
-        <f>TODAY()+25</f>
-        <v>46304.0</v>
+      <c r="E173" s="37" t="n">
+        <v>46304</v>
       </c>
       <c r="F173" s="38" t="n">
         <v>190</v>
@@ -24318,9 +24295,8 @@
       <c r="D174" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E174" s="37">
-        <f>TODAY()+55</f>
-        <v>46334.0</v>
+      <c r="E174" s="37" t="n">
+        <v>46334</v>
       </c>
       <c r="F174" s="38" t="n">
         <v>190</v>
@@ -24377,9 +24353,8 @@
       <c r="D175" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E175" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
+      <c r="E175" s="37" t="n">
+        <v>46305</v>
       </c>
       <c r="F175" s="38" t="n">
         <v>190</v>
@@ -24436,9 +24411,8 @@
       <c r="D176" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E176" s="37">
-        <f>TODAY()+56</f>
-        <v>46335.0</v>
+      <c r="E176" s="37" t="n">
+        <v>46335</v>
       </c>
       <c r="F176" s="38" t="n">
         <v>190</v>
@@ -24495,9 +24469,8 @@
       <c r="D177" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E177" s="37">
-        <f>TODAY()+26</f>
-        <v>46305.0</v>
+      <c r="E177" s="37" t="n">
+        <v>46305</v>
       </c>
       <c r="F177" s="38" t="n">
         <v>400</v>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -33167,19 +33167,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Pacientes!$A$5,0,0,MAX(1,COUNTA(Pacientes!$A$5:$A$404)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A34:G41">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND(ISNUMBER($G34),$G34&lt;=Config!$B$6)</formula>
+      <formula>AND(ISNUMBER($G34),$G34&lt;=INDIRECT("Config!$B$6"))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33155,7 +33155,7 @@
       <formula>$I5="Vencida"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND($I5="A vencer",$K5&lt;=Config!$B$6)</formula>
+      <formula>AND($I5="A vencer",$K5&lt;=INDIRECT("Config!$B$6"))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
       <formula>$I5="Paga"</formula>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/14-parcelas-e-inadimplencia.xlsx
@@ -33139,7 +33139,7 @@
     <row r="406">
       <c r="A406" s="28" t="inlineStr">
         <is>
-          <t>Vermelho: vencida. Amarelo: vence na janela curta. Verde: paga. Data do pagamento em vermelho: marcada como paga sem data. No exemplo, as parcelas pagas têm data fixa (cada uma é uma entrada do caixa, planilha 09) e as em aberto têm vencimento relativo a hoje.</t>
+          <t>Vermelho: vencida. Amarelo: vence na janela curta. Verde: paga. Data do pagamento em vermelho: marcada como paga sem data. No exemplo, as parcelas pagas têm data fixa (cada uma é uma entrada do caixa, planilha 09) e as em aberto têm vencimento em data literal: o exemplo inteiro é uma foto de 14/09/2026 e não se atualiza sozinho. Ao começar com os seus dados, apague o exemplo e lance as suas parcelas.</t>
         </is>
       </c>
     </row>
